--- a/student_record_system/Tests/Student_record_system_test_log.xlsx
+++ b/student_record_system/Tests/Student_record_system_test_log.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qwert\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qwert\Downloads\Magdalaga_Gabriell_CP1P1\student_record_system\Tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4BA12144-B8DC-4A3E-9F56-D46580A8073E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A76757A1-7FFA-4B71-9607-8F90BA7D5BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1119,7 +1119,7 @@
     <t>Add the code in the formatters to show email</t>
   </si>
   <si>
-    <t>Gabriell B. Magdalaga</t>
+    <t>Magdalaga, Gabriell B. &amp; Alvarez, Joel</t>
   </si>
 </sst>
 </file>
@@ -1460,22 +1460,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1484,26 +1506,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1514,24 +1521,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1853,7 +1853,7 @@
     <col min="2" max="2" width="25.90625" customWidth="1"/>
     <col min="3" max="3" width="40.54296875" customWidth="1"/>
     <col min="4" max="4" width="13.6328125" customWidth="1"/>
-    <col min="5" max="5" width="27.36328125" customWidth="1"/>
+    <col min="5" max="5" width="35.26953125" customWidth="1"/>
     <col min="6" max="6" width="23.36328125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1873,7 +1873,7 @@
       <c r="D4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="47">
+      <c r="E4" s="25">
         <v>46057</v>
       </c>
     </row>
@@ -1962,13 +1962,13 @@
       <c r="C6" s="9">
         <v>23</v>
       </c>
-      <c r="D6" s="46">
+      <c r="D6" s="24">
         <v>0.95830000000000004</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="46">
+      <c r="F6" s="24">
         <v>0.95830000000000004</v>
       </c>
       <c r="G6" s="9"/>
@@ -2038,7 +2038,7 @@
       <c r="A2" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="27" t="s">
         <v>40</v>
       </c>
       <c r="C2" s="26" t="s">
@@ -2047,94 +2047,94 @@
       <c r="D2" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="G2" s="27" t="s">
         <v>48</v>
       </c>
       <c r="H2" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="I2" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="J2" s="24" t="s">
+      <c r="J2" s="28" t="s">
         <v>46</v>
       </c>
       <c r="K2" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="L2" s="38"/>
+      <c r="L2" s="41"/>
     </row>
     <row r="3" spans="1:12" ht="49.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="26"/>
-      <c r="B3" s="25"/>
+      <c r="B3" s="27"/>
       <c r="C3" s="26"/>
       <c r="D3" s="26"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
       <c r="H3" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
       <c r="K3" s="26"/>
-      <c r="L3" s="39"/>
+      <c r="L3" s="42"/>
     </row>
     <row r="4" spans="1:12" ht="49.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="26"/>
-      <c r="B4" s="25"/>
+      <c r="B4" s="27"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
       <c r="H4" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
       <c r="K4" s="26"/>
-      <c r="L4" s="39"/>
+      <c r="L4" s="42"/>
     </row>
     <row r="5" spans="1:12" ht="49.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="26"/>
-      <c r="B5" s="25"/>
+      <c r="B5" s="27"/>
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
       <c r="K5" s="26"/>
-      <c r="L5" s="39"/>
+      <c r="L5" s="42"/>
     </row>
     <row r="6" spans="1:12" ht="49.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="26"/>
-      <c r="B6" s="25"/>
+      <c r="B6" s="27"/>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
       <c r="K6" s="26"/>
-      <c r="L6" s="40"/>
+      <c r="L6" s="43"/>
     </row>
     <row r="7" spans="1:12" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="27" t="s">
         <v>45</v>
       </c>
       <c r="C7" s="26" t="s">
@@ -2143,98 +2143,98 @@
       <c r="D7" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="F7" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="27" t="s">
         <v>48</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="I7" s="24" t="s">
+      <c r="I7" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="J7" s="24" t="s">
+      <c r="J7" s="28" t="s">
         <v>56</v>
       </c>
       <c r="K7" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="L7" s="38"/>
+      <c r="L7" s="41"/>
     </row>
     <row r="8" spans="1:12" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="26"/>
-      <c r="B8" s="25"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="26"/>
       <c r="D8" s="26"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
       <c r="H8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
       <c r="K8" s="26"/>
-      <c r="L8" s="39"/>
+      <c r="L8" s="42"/>
     </row>
     <row r="9" spans="1:12" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="26"/>
-      <c r="B9" s="25"/>
+      <c r="B9" s="27"/>
       <c r="C9" s="26"/>
       <c r="D9" s="26"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
       <c r="H9" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
       <c r="K9" s="26"/>
-      <c r="L9" s="39"/>
+      <c r="L9" s="42"/>
     </row>
     <row r="10" spans="1:12" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="26"/>
-      <c r="B10" s="25"/>
+      <c r="B10" s="27"/>
       <c r="C10" s="26"/>
       <c r="D10" s="26"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
       <c r="H10" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
       <c r="K10" s="26"/>
-      <c r="L10" s="39"/>
+      <c r="L10" s="42"/>
     </row>
     <row r="11" spans="1:12" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="26"/>
-      <c r="B11" s="25"/>
+      <c r="B11" s="27"/>
       <c r="C11" s="26"/>
       <c r="D11" s="26"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
       <c r="H11" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27"/>
       <c r="K11" s="26"/>
-      <c r="L11" s="40"/>
+      <c r="L11" s="43"/>
     </row>
     <row r="12" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="27" t="s">
         <v>58</v>
       </c>
       <c r="C12" s="26" t="s">
@@ -2243,98 +2243,98 @@
       <c r="D12" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="24" t="s">
+      <c r="F12" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G12" s="27" t="s">
         <v>66</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="I12" s="24" t="s">
+      <c r="I12" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="J12" s="43" t="s">
+      <c r="J12" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="K12" s="27" t="s">
+      <c r="K12" s="34" t="s">
         <v>280</v>
       </c>
-      <c r="L12" s="29"/>
+      <c r="L12" s="37"/>
     </row>
     <row r="13" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="26"/>
-      <c r="B13" s="25"/>
+      <c r="B13" s="27"/>
       <c r="C13" s="26"/>
       <c r="D13" s="26"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
       <c r="H13" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="I13" s="25"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="30"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="38"/>
     </row>
     <row r="14" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="26"/>
-      <c r="B14" s="25"/>
+      <c r="B14" s="27"/>
       <c r="C14" s="26"/>
       <c r="D14" s="26"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
       <c r="H14" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="I14" s="25"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="28"/>
-      <c r="L14" s="30"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="35"/>
+      <c r="L14" s="38"/>
     </row>
     <row r="15" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="26"/>
-      <c r="B15" s="25"/>
+      <c r="B15" s="27"/>
       <c r="C15" s="26"/>
       <c r="D15" s="26"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
       <c r="H15" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="I15" s="25"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="30"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="38"/>
     </row>
     <row r="16" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="26"/>
-      <c r="B16" s="25"/>
+      <c r="B16" s="27"/>
       <c r="C16" s="26"/>
       <c r="D16" s="26"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
       <c r="H16" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="I16" s="25"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="37"/>
-      <c r="L16" s="35"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="36"/>
+      <c r="L16" s="39"/>
     </row>
     <row r="17" spans="1:12" ht="22.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="27" t="s">
         <v>68</v>
       </c>
       <c r="C17" s="26" t="s">
@@ -2343,130 +2343,130 @@
       <c r="D17" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="F17" s="24" t="s">
+      <c r="F17" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="G17" s="41" t="s">
+      <c r="G17" s="32" t="s">
         <v>99</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="I17" s="31" t="s">
+      <c r="I17" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="J17" s="31" t="s">
+      <c r="J17" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="K17" s="27" t="s">
+      <c r="K17" s="34" t="s">
         <v>280</v>
       </c>
-      <c r="L17" s="29"/>
+      <c r="L17" s="37"/>
     </row>
     <row r="18" spans="1:12" ht="22.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="26"/>
-      <c r="B18" s="25"/>
+      <c r="B18" s="27"/>
       <c r="C18" s="26"/>
       <c r="D18" s="26"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="42"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="33"/>
       <c r="H18" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="38"/>
     </row>
     <row r="19" spans="1:12" ht="22.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="26"/>
-      <c r="B19" s="25"/>
+      <c r="B19" s="27"/>
       <c r="C19" s="26"/>
       <c r="D19" s="26"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="42"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="33"/>
       <c r="H19" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="38"/>
     </row>
     <row r="20" spans="1:12" ht="22.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="26"/>
-      <c r="B20" s="25"/>
+      <c r="B20" s="27"/>
       <c r="C20" s="26"/>
       <c r="D20" s="26"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="42"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="33"/>
       <c r="H20" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="I20" s="32"/>
-      <c r="J20" s="32"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="38"/>
     </row>
     <row r="21" spans="1:12" ht="22.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="26"/>
-      <c r="B21" s="25"/>
+      <c r="B21" s="27"/>
       <c r="C21" s="26"/>
       <c r="D21" s="26"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="42"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="33"/>
       <c r="H21" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="38"/>
     </row>
     <row r="22" spans="1:12" ht="22.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="26"/>
-      <c r="B22" s="25"/>
+      <c r="B22" s="27"/>
       <c r="C22" s="26"/>
       <c r="D22" s="26"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="42"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="33"/>
       <c r="H22" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="38"/>
     </row>
     <row r="23" spans="1:12" ht="34.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="26"/>
-      <c r="B23" s="25"/>
+      <c r="B23" s="27"/>
       <c r="C23" s="26"/>
       <c r="D23" s="26"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="42"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="33"/>
       <c r="H23" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="I23" s="36"/>
-      <c r="J23" s="36"/>
-      <c r="K23" s="37"/>
-      <c r="L23" s="35"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="36"/>
+      <c r="L23" s="39"/>
     </row>
     <row r="24" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="B24" s="25" t="s">
+      <c r="B24" s="27" t="s">
         <v>83</v>
       </c>
       <c r="C24" s="26" t="s">
@@ -2475,130 +2475,130 @@
       <c r="D24" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="F24" s="24" t="s">
+      <c r="F24" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="G24" s="31" t="s">
+      <c r="G24" s="29" t="s">
         <v>96</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="I24" s="31" t="s">
+      <c r="I24" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="J24" s="31" t="s">
+      <c r="J24" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="K24" s="27" t="s">
+      <c r="K24" s="34" t="s">
         <v>280</v>
       </c>
-      <c r="L24" s="29"/>
+      <c r="L24" s="37"/>
     </row>
     <row r="25" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="26"/>
-      <c r="B25" s="25"/>
+      <c r="B25" s="27"/>
       <c r="C25" s="26"/>
       <c r="D25" s="26"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="32"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="30"/>
       <c r="H25" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="35"/>
+      <c r="L25" s="38"/>
     </row>
     <row r="26" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="26"/>
-      <c r="B26" s="25"/>
+      <c r="B26" s="27"/>
       <c r="C26" s="26"/>
       <c r="D26" s="26"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="32"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="30"/>
       <c r="H26" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="35"/>
+      <c r="L26" s="38"/>
     </row>
     <row r="27" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="26"/>
-      <c r="B27" s="25"/>
+      <c r="B27" s="27"/>
       <c r="C27" s="26"/>
       <c r="D27" s="26"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="32"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="30"/>
       <c r="H27" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="30"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="35"/>
+      <c r="L27" s="38"/>
     </row>
     <row r="28" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="26"/>
-      <c r="B28" s="25"/>
+      <c r="B28" s="27"/>
       <c r="C28" s="26"/>
       <c r="D28" s="26"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="32"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="30"/>
       <c r="H28" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I28" s="32"/>
-      <c r="J28" s="32"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="35"/>
+      <c r="L28" s="38"/>
     </row>
     <row r="29" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="26"/>
-      <c r="B29" s="25"/>
+      <c r="B29" s="27"/>
       <c r="C29" s="26"/>
       <c r="D29" s="26"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="32"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="30"/>
       <c r="H29" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="I29" s="32"/>
-      <c r="J29" s="32"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="35"/>
+      <c r="L29" s="38"/>
     </row>
     <row r="30" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="26"/>
-      <c r="B30" s="25"/>
+      <c r="B30" s="27"/>
       <c r="C30" s="26"/>
       <c r="D30" s="26"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="36"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="31"/>
       <c r="H30" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="I30" s="36"/>
-      <c r="J30" s="36"/>
-      <c r="K30" s="37"/>
-      <c r="L30" s="35"/>
+      <c r="I30" s="31"/>
+      <c r="J30" s="31"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="39"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="B31" s="25" t="s">
+      <c r="B31" s="27" t="s">
         <v>95</v>
       </c>
       <c r="C31" s="26" t="s">
@@ -2607,126 +2607,126 @@
       <c r="D31" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="E31" s="24" t="s">
+      <c r="E31" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="F31" s="24" t="s">
+      <c r="F31" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="G31" s="31" t="s">
+      <c r="G31" s="29" t="s">
         <v>98</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="I31" s="31" t="s">
+      <c r="I31" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="J31" s="43" t="s">
+      <c r="J31" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="K31" s="27" t="s">
+      <c r="K31" s="34" t="s">
         <v>280</v>
       </c>
-      <c r="L31" s="29"/>
+      <c r="L31" s="37"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" s="26"/>
-      <c r="B32" s="25"/>
+      <c r="B32" s="27"/>
       <c r="C32" s="26"/>
       <c r="D32" s="26"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="32"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="30"/>
       <c r="H32" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="I32" s="32"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="38"/>
+      <c r="K32" s="35"/>
+      <c r="L32" s="38"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="26"/>
-      <c r="B33" s="25"/>
+      <c r="B33" s="27"/>
       <c r="C33" s="26"/>
       <c r="D33" s="26"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="32"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="30"/>
       <c r="H33" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="I33" s="32"/>
-      <c r="J33" s="30"/>
-      <c r="K33" s="28"/>
-      <c r="L33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="38"/>
+      <c r="K33" s="35"/>
+      <c r="L33" s="38"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="26"/>
-      <c r="B34" s="25"/>
+      <c r="B34" s="27"/>
       <c r="C34" s="26"/>
       <c r="D34" s="26"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="32"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="30"/>
       <c r="H34" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="I34" s="32"/>
-      <c r="J34" s="30"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="38"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="38"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="26"/>
-      <c r="B35" s="25"/>
+      <c r="B35" s="27"/>
       <c r="C35" s="26"/>
       <c r="D35" s="26"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="32"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="30"/>
       <c r="H35" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="I35" s="32"/>
-      <c r="J35" s="30"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="38"/>
+      <c r="K35" s="35"/>
+      <c r="L35" s="38"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" s="26"/>
-      <c r="B36" s="25"/>
+      <c r="B36" s="27"/>
       <c r="C36" s="26"/>
       <c r="D36" s="26"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="32"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="30"/>
       <c r="H36" s="3"/>
-      <c r="I36" s="32"/>
-      <c r="J36" s="30"/>
-      <c r="K36" s="28"/>
-      <c r="L36" s="30"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="38"/>
+      <c r="K36" s="35"/>
+      <c r="L36" s="38"/>
     </row>
     <row r="37" spans="1:12" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="26"/>
-      <c r="B37" s="25"/>
+      <c r="B37" s="27"/>
       <c r="C37" s="26"/>
       <c r="D37" s="26"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="36"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="31"/>
       <c r="H37" s="3"/>
-      <c r="I37" s="36"/>
-      <c r="J37" s="35"/>
-      <c r="K37" s="37"/>
-      <c r="L37" s="35"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="39"/>
+      <c r="K37" s="36"/>
+      <c r="L37" s="39"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B38" s="27" t="s">
         <v>215</v>
       </c>
       <c r="C38" s="26" t="s">
@@ -2735,78 +2735,78 @@
       <c r="D38" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="E38" s="24" t="s">
+      <c r="E38" s="28" t="s">
         <v>216</v>
       </c>
-      <c r="F38" s="24" t="s">
+      <c r="F38" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="G38" s="31" t="s">
+      <c r="G38" s="29" t="s">
         <v>217</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="I38" s="31" t="s">
+      <c r="I38" s="29" t="s">
         <v>220</v>
       </c>
-      <c r="J38" s="43" t="s">
+      <c r="J38" s="40" t="s">
         <v>220</v>
       </c>
-      <c r="K38" s="27" t="s">
+      <c r="K38" s="34" t="s">
         <v>280</v>
       </c>
-      <c r="L38" s="29"/>
+      <c r="L38" s="37"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="26"/>
-      <c r="B39" s="25"/>
+      <c r="B39" s="27"/>
       <c r="C39" s="26"/>
       <c r="D39" s="26"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="32"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="30"/>
       <c r="H39" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="I39" s="32"/>
-      <c r="J39" s="30"/>
-      <c r="K39" s="28"/>
-      <c r="L39" s="30"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="38"/>
+      <c r="K39" s="35"/>
+      <c r="L39" s="38"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="26"/>
-      <c r="B40" s="25"/>
+      <c r="B40" s="27"/>
       <c r="C40" s="26"/>
       <c r="D40" s="26"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="32"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="30"/>
       <c r="H40" s="3"/>
-      <c r="I40" s="32"/>
-      <c r="J40" s="30"/>
-      <c r="K40" s="28"/>
-      <c r="L40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="38"/>
+      <c r="K40" s="35"/>
+      <c r="L40" s="38"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="26"/>
-      <c r="B41" s="25"/>
+      <c r="B41" s="27"/>
       <c r="C41" s="26"/>
       <c r="D41" s="26"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="32"/>
+      <c r="E41" s="28"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="30"/>
       <c r="H41" s="3"/>
-      <c r="I41" s="32"/>
-      <c r="J41" s="30"/>
-      <c r="K41" s="28"/>
-      <c r="L41" s="30"/>
+      <c r="I41" s="30"/>
+      <c r="J41" s="38"/>
+      <c r="K41" s="35"/>
+      <c r="L41" s="38"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="B42" s="24" t="s">
+      <c r="B42" s="28" t="s">
         <v>109</v>
       </c>
       <c r="C42" s="26" t="s">
@@ -2815,162 +2815,162 @@
       <c r="D42" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="E42" s="24" t="s">
+      <c r="E42" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="F42" s="24" t="s">
+      <c r="F42" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="G42" s="31" t="s">
+      <c r="G42" s="29" t="s">
         <v>111</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="I42" s="31" t="s">
+      <c r="I42" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="J42" s="31" t="s">
+      <c r="J42" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="K42" s="27" t="s">
+      <c r="K42" s="34" t="s">
         <v>280</v>
       </c>
-      <c r="L42" s="29"/>
+      <c r="L42" s="37"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="26"/>
-      <c r="B43" s="24"/>
+      <c r="B43" s="28"/>
       <c r="C43" s="26"/>
       <c r="D43" s="26"/>
-      <c r="E43" s="24"/>
-      <c r="F43" s="25"/>
-      <c r="G43" s="32"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="30"/>
       <c r="H43" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="I43" s="32"/>
-      <c r="J43" s="32"/>
-      <c r="K43" s="28"/>
-      <c r="L43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="35"/>
+      <c r="L43" s="38"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="26"/>
-      <c r="B44" s="24"/>
+      <c r="B44" s="28"/>
       <c r="C44" s="26"/>
       <c r="D44" s="26"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="25"/>
-      <c r="G44" s="32"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="30"/>
       <c r="H44" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="I44" s="32"/>
-      <c r="J44" s="32"/>
-      <c r="K44" s="28"/>
-      <c r="L44" s="30"/>
+      <c r="I44" s="30"/>
+      <c r="J44" s="30"/>
+      <c r="K44" s="35"/>
+      <c r="L44" s="38"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" s="26"/>
-      <c r="B45" s="24"/>
+      <c r="B45" s="28"/>
       <c r="C45" s="26"/>
       <c r="D45" s="26"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="32"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="27"/>
+      <c r="G45" s="30"/>
       <c r="H45" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="I45" s="32"/>
-      <c r="J45" s="32"/>
-      <c r="K45" s="28"/>
-      <c r="L45" s="30"/>
+      <c r="I45" s="30"/>
+      <c r="J45" s="30"/>
+      <c r="K45" s="35"/>
+      <c r="L45" s="38"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="26"/>
-      <c r="B46" s="24"/>
+      <c r="B46" s="28"/>
       <c r="C46" s="26"/>
       <c r="D46" s="26"/>
-      <c r="E46" s="24"/>
-      <c r="F46" s="25"/>
-      <c r="G46" s="32"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="30"/>
       <c r="H46" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="I46" s="32"/>
-      <c r="J46" s="32"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="35"/>
+      <c r="L46" s="38"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" s="26"/>
-      <c r="B47" s="24"/>
+      <c r="B47" s="28"/>
       <c r="C47" s="26"/>
       <c r="D47" s="26"/>
-      <c r="E47" s="24"/>
-      <c r="F47" s="25"/>
-      <c r="G47" s="32"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="27"/>
+      <c r="G47" s="30"/>
       <c r="H47" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="I47" s="32"/>
-      <c r="J47" s="32"/>
-      <c r="K47" s="28"/>
-      <c r="L47" s="30"/>
+      <c r="I47" s="30"/>
+      <c r="J47" s="30"/>
+      <c r="K47" s="35"/>
+      <c r="L47" s="38"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="26"/>
-      <c r="B48" s="24"/>
+      <c r="B48" s="28"/>
       <c r="C48" s="26"/>
       <c r="D48" s="26"/>
-      <c r="E48" s="24"/>
-      <c r="F48" s="25"/>
-      <c r="G48" s="32"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="27"/>
+      <c r="G48" s="30"/>
       <c r="H48" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="I48" s="32"/>
-      <c r="J48" s="32"/>
-      <c r="K48" s="28"/>
-      <c r="L48" s="30"/>
+      <c r="I48" s="30"/>
+      <c r="J48" s="30"/>
+      <c r="K48" s="35"/>
+      <c r="L48" s="38"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" s="26"/>
-      <c r="B49" s="24"/>
+      <c r="B49" s="28"/>
       <c r="C49" s="26"/>
       <c r="D49" s="26"/>
-      <c r="E49" s="24"/>
-      <c r="F49" s="25"/>
-      <c r="G49" s="32"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="30"/>
       <c r="H49" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="I49" s="32"/>
-      <c r="J49" s="32"/>
-      <c r="K49" s="28"/>
-      <c r="L49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="35"/>
+      <c r="L49" s="38"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" s="26"/>
-      <c r="B50" s="24"/>
+      <c r="B50" s="28"/>
       <c r="C50" s="26"/>
       <c r="D50" s="26"/>
-      <c r="E50" s="24"/>
-      <c r="F50" s="25"/>
-      <c r="G50" s="36"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="27"/>
+      <c r="G50" s="31"/>
       <c r="H50" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="I50" s="36"/>
-      <c r="J50" s="36"/>
-      <c r="K50" s="37"/>
-      <c r="L50" s="35"/>
+      <c r="I50" s="31"/>
+      <c r="J50" s="31"/>
+      <c r="K50" s="36"/>
+      <c r="L50" s="39"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" s="26" t="s">
         <v>221</v>
       </c>
-      <c r="B51" s="24" t="s">
+      <c r="B51" s="28" t="s">
         <v>122</v>
       </c>
       <c r="C51" s="26" t="s">
@@ -2979,178 +2979,178 @@
       <c r="D51" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E51" s="24" t="s">
+      <c r="E51" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="F51" s="24" t="s">
+      <c r="F51" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="G51" s="31" t="s">
+      <c r="G51" s="29" t="s">
         <v>124</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="I51" s="31" t="s">
+      <c r="I51" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="J51" s="31" t="s">
+      <c r="J51" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="K51" s="27" t="s">
+      <c r="K51" s="34" t="s">
         <v>280</v>
       </c>
-      <c r="L51" s="29"/>
+      <c r="L51" s="37"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" s="26"/>
-      <c r="B52" s="24"/>
+      <c r="B52" s="28"/>
       <c r="C52" s="26"/>
       <c r="D52" s="26"/>
-      <c r="E52" s="24"/>
-      <c r="F52" s="25"/>
-      <c r="G52" s="32"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="27"/>
+      <c r="G52" s="30"/>
       <c r="H52" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="I52" s="32"/>
-      <c r="J52" s="32"/>
-      <c r="K52" s="28"/>
-      <c r="L52" s="30"/>
+      <c r="I52" s="30"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="35"/>
+      <c r="L52" s="38"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" s="26"/>
-      <c r="B53" s="24"/>
+      <c r="B53" s="28"/>
       <c r="C53" s="26"/>
       <c r="D53" s="26"/>
-      <c r="E53" s="24"/>
-      <c r="F53" s="25"/>
-      <c r="G53" s="32"/>
+      <c r="E53" s="28"/>
+      <c r="F53" s="27"/>
+      <c r="G53" s="30"/>
       <c r="H53" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="I53" s="32"/>
-      <c r="J53" s="32"/>
-      <c r="K53" s="28"/>
-      <c r="L53" s="30"/>
+      <c r="I53" s="30"/>
+      <c r="J53" s="30"/>
+      <c r="K53" s="35"/>
+      <c r="L53" s="38"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" s="26"/>
-      <c r="B54" s="24"/>
+      <c r="B54" s="28"/>
       <c r="C54" s="26"/>
       <c r="D54" s="26"/>
-      <c r="E54" s="24"/>
-      <c r="F54" s="25"/>
-      <c r="G54" s="32"/>
+      <c r="E54" s="28"/>
+      <c r="F54" s="27"/>
+      <c r="G54" s="30"/>
       <c r="H54" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="I54" s="32"/>
-      <c r="J54" s="32"/>
-      <c r="K54" s="28"/>
-      <c r="L54" s="30"/>
+      <c r="I54" s="30"/>
+      <c r="J54" s="30"/>
+      <c r="K54" s="35"/>
+      <c r="L54" s="38"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" s="26"/>
-      <c r="B55" s="24"/>
+      <c r="B55" s="28"/>
       <c r="C55" s="26"/>
       <c r="D55" s="26"/>
-      <c r="E55" s="24"/>
-      <c r="F55" s="25"/>
-      <c r="G55" s="32"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="27"/>
+      <c r="G55" s="30"/>
       <c r="H55" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="I55" s="32"/>
-      <c r="J55" s="32"/>
-      <c r="K55" s="28"/>
-      <c r="L55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="35"/>
+      <c r="L55" s="38"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" s="26"/>
-      <c r="B56" s="24"/>
+      <c r="B56" s="28"/>
       <c r="C56" s="26"/>
       <c r="D56" s="26"/>
-      <c r="E56" s="24"/>
-      <c r="F56" s="25"/>
-      <c r="G56" s="32"/>
+      <c r="E56" s="28"/>
+      <c r="F56" s="27"/>
+      <c r="G56" s="30"/>
       <c r="H56" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="I56" s="32"/>
-      <c r="J56" s="32"/>
-      <c r="K56" s="28"/>
-      <c r="L56" s="30"/>
+      <c r="I56" s="30"/>
+      <c r="J56" s="30"/>
+      <c r="K56" s="35"/>
+      <c r="L56" s="38"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" s="26"/>
-      <c r="B57" s="24"/>
+      <c r="B57" s="28"/>
       <c r="C57" s="26"/>
       <c r="D57" s="26"/>
-      <c r="E57" s="24"/>
-      <c r="F57" s="25"/>
-      <c r="G57" s="32"/>
+      <c r="E57" s="28"/>
+      <c r="F57" s="27"/>
+      <c r="G57" s="30"/>
       <c r="H57" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="I57" s="32"/>
-      <c r="J57" s="32"/>
-      <c r="K57" s="28"/>
-      <c r="L57" s="30"/>
+      <c r="I57" s="30"/>
+      <c r="J57" s="30"/>
+      <c r="K57" s="35"/>
+      <c r="L57" s="38"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" s="26"/>
-      <c r="B58" s="24"/>
+      <c r="B58" s="28"/>
       <c r="C58" s="26"/>
       <c r="D58" s="26"/>
-      <c r="E58" s="24"/>
-      <c r="F58" s="25"/>
-      <c r="G58" s="32"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="27"/>
+      <c r="G58" s="30"/>
       <c r="H58" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="I58" s="32"/>
-      <c r="J58" s="32"/>
-      <c r="K58" s="28"/>
-      <c r="L58" s="30"/>
+      <c r="I58" s="30"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="35"/>
+      <c r="L58" s="38"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59" s="26"/>
-      <c r="B59" s="24"/>
+      <c r="B59" s="28"/>
       <c r="C59" s="26"/>
       <c r="D59" s="26"/>
-      <c r="E59" s="24"/>
-      <c r="F59" s="25"/>
-      <c r="G59" s="32"/>
+      <c r="E59" s="28"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="30"/>
       <c r="H59" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="I59" s="32"/>
-      <c r="J59" s="32"/>
-      <c r="K59" s="28"/>
-      <c r="L59" s="30"/>
+      <c r="I59" s="30"/>
+      <c r="J59" s="30"/>
+      <c r="K59" s="35"/>
+      <c r="L59" s="38"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" s="26"/>
-      <c r="B60" s="24"/>
+      <c r="B60" s="28"/>
       <c r="C60" s="26"/>
       <c r="D60" s="26"/>
-      <c r="E60" s="24"/>
-      <c r="F60" s="25"/>
-      <c r="G60" s="36"/>
+      <c r="E60" s="28"/>
+      <c r="F60" s="27"/>
+      <c r="G60" s="31"/>
       <c r="H60" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="I60" s="36"/>
-      <c r="J60" s="36"/>
-      <c r="K60" s="37"/>
-      <c r="L60" s="35"/>
+      <c r="I60" s="31"/>
+      <c r="J60" s="31"/>
+      <c r="K60" s="36"/>
+      <c r="L60" s="39"/>
     </row>
     <row r="61" spans="1:12" ht="29.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="26" t="s">
         <v>222</v>
       </c>
-      <c r="B61" s="25" t="s">
+      <c r="B61" s="27" t="s">
         <v>223</v>
       </c>
       <c r="C61" s="26" t="s">
@@ -3159,78 +3159,78 @@
       <c r="D61" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="E61" s="24" t="s">
+      <c r="E61" s="28" t="s">
         <v>224</v>
       </c>
-      <c r="F61" s="24" t="s">
+      <c r="F61" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="G61" s="31" t="s">
+      <c r="G61" s="29" t="s">
         <v>226</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="I61" s="31" t="s">
+      <c r="I61" s="29" t="s">
         <v>227</v>
       </c>
-      <c r="J61" s="31" t="s">
+      <c r="J61" s="29" t="s">
         <v>281</v>
       </c>
-      <c r="K61" s="27" t="s">
+      <c r="K61" s="34" t="s">
         <v>280</v>
       </c>
-      <c r="L61" s="29"/>
+      <c r="L61" s="37"/>
     </row>
     <row r="62" spans="1:12" ht="29.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="26"/>
-      <c r="B62" s="25"/>
+      <c r="B62" s="27"/>
       <c r="C62" s="26"/>
       <c r="D62" s="26"/>
-      <c r="E62" s="24"/>
-      <c r="F62" s="25"/>
-      <c r="G62" s="32"/>
+      <c r="E62" s="28"/>
+      <c r="F62" s="27"/>
+      <c r="G62" s="30"/>
       <c r="H62" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="I62" s="32"/>
-      <c r="J62" s="32"/>
-      <c r="K62" s="28"/>
-      <c r="L62" s="30"/>
+      <c r="I62" s="30"/>
+      <c r="J62" s="30"/>
+      <c r="K62" s="35"/>
+      <c r="L62" s="38"/>
     </row>
     <row r="63" spans="1:12" ht="29.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="26"/>
-      <c r="B63" s="25"/>
+      <c r="B63" s="27"/>
       <c r="C63" s="26"/>
       <c r="D63" s="26"/>
-      <c r="E63" s="24"/>
-      <c r="F63" s="25"/>
-      <c r="G63" s="32"/>
+      <c r="E63" s="28"/>
+      <c r="F63" s="27"/>
+      <c r="G63" s="30"/>
       <c r="H63" s="3"/>
-      <c r="I63" s="32"/>
-      <c r="J63" s="32"/>
-      <c r="K63" s="28"/>
-      <c r="L63" s="30"/>
+      <c r="I63" s="30"/>
+      <c r="J63" s="30"/>
+      <c r="K63" s="35"/>
+      <c r="L63" s="38"/>
     </row>
     <row r="64" spans="1:12" ht="29.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="26"/>
-      <c r="B64" s="25"/>
+      <c r="B64" s="27"/>
       <c r="C64" s="26"/>
       <c r="D64" s="26"/>
-      <c r="E64" s="24"/>
-      <c r="F64" s="25"/>
-      <c r="G64" s="32"/>
+      <c r="E64" s="28"/>
+      <c r="F64" s="27"/>
+      <c r="G64" s="30"/>
       <c r="H64" s="3"/>
-      <c r="I64" s="32"/>
-      <c r="J64" s="32"/>
-      <c r="K64" s="28"/>
-      <c r="L64" s="30"/>
+      <c r="I64" s="30"/>
+      <c r="J64" s="30"/>
+      <c r="K64" s="35"/>
+      <c r="L64" s="38"/>
     </row>
     <row r="65" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A65" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="B65" s="25" t="s">
+      <c r="B65" s="27" t="s">
         <v>137</v>
       </c>
       <c r="C65" s="26" t="s">
@@ -3239,122 +3239,122 @@
       <c r="D65" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="E65" s="24" t="s">
+      <c r="E65" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="F65" s="24" t="s">
+      <c r="F65" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="G65" s="31" t="s">
+      <c r="G65" s="29" t="s">
         <v>151</v>
       </c>
       <c r="H65" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="I65" s="31" t="s">
+      <c r="I65" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="J65" s="24" t="s">
+      <c r="J65" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="K65" s="27" t="s">
+      <c r="K65" s="34" t="s">
         <v>280</v>
       </c>
-      <c r="L65" s="29"/>
+      <c r="L65" s="37"/>
     </row>
     <row r="66" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A66" s="26"/>
-      <c r="B66" s="25"/>
+      <c r="B66" s="27"/>
       <c r="C66" s="26"/>
       <c r="D66" s="26"/>
-      <c r="E66" s="24"/>
-      <c r="F66" s="25"/>
-      <c r="G66" s="33"/>
+      <c r="E66" s="28"/>
+      <c r="F66" s="27"/>
+      <c r="G66" s="44"/>
       <c r="H66" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="I66" s="32"/>
-      <c r="J66" s="25"/>
-      <c r="K66" s="28"/>
-      <c r="L66" s="30"/>
+      <c r="I66" s="30"/>
+      <c r="J66" s="27"/>
+      <c r="K66" s="35"/>
+      <c r="L66" s="38"/>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A67" s="26"/>
-      <c r="B67" s="25"/>
+      <c r="B67" s="27"/>
       <c r="C67" s="26"/>
       <c r="D67" s="26"/>
-      <c r="E67" s="24"/>
-      <c r="F67" s="25"/>
-      <c r="G67" s="33"/>
+      <c r="E67" s="28"/>
+      <c r="F67" s="27"/>
+      <c r="G67" s="44"/>
       <c r="H67" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="I67" s="32"/>
-      <c r="J67" s="25"/>
-      <c r="K67" s="28"/>
-      <c r="L67" s="30"/>
+      <c r="I67" s="30"/>
+      <c r="J67" s="27"/>
+      <c r="K67" s="35"/>
+      <c r="L67" s="38"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A68" s="26"/>
-      <c r="B68" s="25"/>
+      <c r="B68" s="27"/>
       <c r="C68" s="26"/>
       <c r="D68" s="26"/>
-      <c r="E68" s="24"/>
-      <c r="F68" s="25"/>
-      <c r="G68" s="33"/>
+      <c r="E68" s="28"/>
+      <c r="F68" s="27"/>
+      <c r="G68" s="44"/>
       <c r="H68" s="3"/>
-      <c r="I68" s="32"/>
-      <c r="J68" s="25"/>
-      <c r="K68" s="28"/>
-      <c r="L68" s="30"/>
+      <c r="I68" s="30"/>
+      <c r="J68" s="27"/>
+      <c r="K68" s="35"/>
+      <c r="L68" s="38"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69" s="26"/>
-      <c r="B69" s="25"/>
+      <c r="B69" s="27"/>
       <c r="C69" s="26"/>
       <c r="D69" s="26"/>
-      <c r="E69" s="24"/>
-      <c r="F69" s="25"/>
-      <c r="G69" s="33"/>
+      <c r="E69" s="28"/>
+      <c r="F69" s="27"/>
+      <c r="G69" s="44"/>
       <c r="H69" s="3"/>
-      <c r="I69" s="32"/>
-      <c r="J69" s="25"/>
-      <c r="K69" s="28"/>
-      <c r="L69" s="30"/>
+      <c r="I69" s="30"/>
+      <c r="J69" s="27"/>
+      <c r="K69" s="35"/>
+      <c r="L69" s="38"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A70" s="26"/>
-      <c r="B70" s="25"/>
+      <c r="B70" s="27"/>
       <c r="C70" s="26"/>
       <c r="D70" s="26"/>
-      <c r="E70" s="24"/>
-      <c r="F70" s="25"/>
-      <c r="G70" s="33"/>
+      <c r="E70" s="28"/>
+      <c r="F70" s="27"/>
+      <c r="G70" s="44"/>
       <c r="H70" s="3"/>
-      <c r="I70" s="32"/>
-      <c r="J70" s="25"/>
-      <c r="K70" s="28"/>
-      <c r="L70" s="30"/>
+      <c r="I70" s="30"/>
+      <c r="J70" s="27"/>
+      <c r="K70" s="35"/>
+      <c r="L70" s="38"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71" s="26"/>
-      <c r="B71" s="25"/>
+      <c r="B71" s="27"/>
       <c r="C71" s="26"/>
       <c r="D71" s="26"/>
-      <c r="E71" s="24"/>
-      <c r="F71" s="25"/>
-      <c r="G71" s="34"/>
+      <c r="E71" s="28"/>
+      <c r="F71" s="27"/>
+      <c r="G71" s="45"/>
       <c r="H71" s="3"/>
-      <c r="I71" s="36"/>
-      <c r="J71" s="25"/>
-      <c r="K71" s="37"/>
-      <c r="L71" s="35"/>
+      <c r="I71" s="31"/>
+      <c r="J71" s="27"/>
+      <c r="K71" s="36"/>
+      <c r="L71" s="39"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="B72" s="25" t="s">
+      <c r="B72" s="27" t="s">
         <v>145</v>
       </c>
       <c r="C72" s="26" t="s">
@@ -3363,122 +3363,122 @@
       <c r="D72" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="E72" s="24" t="s">
+      <c r="E72" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="F72" s="24" t="s">
+      <c r="F72" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="G72" s="31" t="s">
+      <c r="G72" s="29" t="s">
         <v>150</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="I72" s="31" t="s">
+      <c r="I72" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="J72" s="24" t="s">
+      <c r="J72" s="28" t="s">
         <v>152</v>
       </c>
-      <c r="K72" s="27" t="s">
+      <c r="K72" s="34" t="s">
         <v>280</v>
       </c>
-      <c r="L72" s="29"/>
+      <c r="L72" s="37"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73" s="26"/>
-      <c r="B73" s="25"/>
+      <c r="B73" s="27"/>
       <c r="C73" s="26"/>
       <c r="D73" s="26"/>
-      <c r="E73" s="24"/>
-      <c r="F73" s="25"/>
-      <c r="G73" s="33"/>
+      <c r="E73" s="28"/>
+      <c r="F73" s="27"/>
+      <c r="G73" s="44"/>
       <c r="H73" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="I73" s="32"/>
-      <c r="J73" s="25"/>
-      <c r="K73" s="28"/>
-      <c r="L73" s="30"/>
+      <c r="I73" s="30"/>
+      <c r="J73" s="27"/>
+      <c r="K73" s="35"/>
+      <c r="L73" s="38"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A74" s="26"/>
-      <c r="B74" s="25"/>
+      <c r="B74" s="27"/>
       <c r="C74" s="26"/>
       <c r="D74" s="26"/>
-      <c r="E74" s="24"/>
-      <c r="F74" s="25"/>
-      <c r="G74" s="33"/>
+      <c r="E74" s="28"/>
+      <c r="F74" s="27"/>
+      <c r="G74" s="44"/>
       <c r="H74" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="I74" s="32"/>
-      <c r="J74" s="25"/>
-      <c r="K74" s="28"/>
-      <c r="L74" s="30"/>
+      <c r="I74" s="30"/>
+      <c r="J74" s="27"/>
+      <c r="K74" s="35"/>
+      <c r="L74" s="38"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A75" s="26"/>
-      <c r="B75" s="25"/>
+      <c r="B75" s="27"/>
       <c r="C75" s="26"/>
       <c r="D75" s="26"/>
-      <c r="E75" s="24"/>
-      <c r="F75" s="25"/>
-      <c r="G75" s="33"/>
+      <c r="E75" s="28"/>
+      <c r="F75" s="27"/>
+      <c r="G75" s="44"/>
       <c r="H75" s="3"/>
-      <c r="I75" s="32"/>
-      <c r="J75" s="25"/>
-      <c r="K75" s="28"/>
-      <c r="L75" s="30"/>
+      <c r="I75" s="30"/>
+      <c r="J75" s="27"/>
+      <c r="K75" s="35"/>
+      <c r="L75" s="38"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A76" s="26"/>
-      <c r="B76" s="25"/>
+      <c r="B76" s="27"/>
       <c r="C76" s="26"/>
       <c r="D76" s="26"/>
-      <c r="E76" s="24"/>
-      <c r="F76" s="25"/>
-      <c r="G76" s="33"/>
+      <c r="E76" s="28"/>
+      <c r="F76" s="27"/>
+      <c r="G76" s="44"/>
       <c r="H76" s="3"/>
-      <c r="I76" s="32"/>
-      <c r="J76" s="25"/>
-      <c r="K76" s="28"/>
-      <c r="L76" s="30"/>
+      <c r="I76" s="30"/>
+      <c r="J76" s="27"/>
+      <c r="K76" s="35"/>
+      <c r="L76" s="38"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A77" s="26"/>
-      <c r="B77" s="25"/>
+      <c r="B77" s="27"/>
       <c r="C77" s="26"/>
       <c r="D77" s="26"/>
-      <c r="E77" s="24"/>
-      <c r="F77" s="25"/>
-      <c r="G77" s="33"/>
+      <c r="E77" s="28"/>
+      <c r="F77" s="27"/>
+      <c r="G77" s="44"/>
       <c r="H77" s="3"/>
-      <c r="I77" s="32"/>
-      <c r="J77" s="25"/>
-      <c r="K77" s="28"/>
-      <c r="L77" s="30"/>
+      <c r="I77" s="30"/>
+      <c r="J77" s="27"/>
+      <c r="K77" s="35"/>
+      <c r="L77" s="38"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A78" s="26"/>
-      <c r="B78" s="25"/>
+      <c r="B78" s="27"/>
       <c r="C78" s="26"/>
       <c r="D78" s="26"/>
-      <c r="E78" s="24"/>
-      <c r="F78" s="25"/>
-      <c r="G78" s="34"/>
+      <c r="E78" s="28"/>
+      <c r="F78" s="27"/>
+      <c r="G78" s="45"/>
       <c r="H78" s="3"/>
-      <c r="I78" s="36"/>
-      <c r="J78" s="25"/>
-      <c r="K78" s="37"/>
-      <c r="L78" s="35"/>
+      <c r="I78" s="31"/>
+      <c r="J78" s="27"/>
+      <c r="K78" s="36"/>
+      <c r="L78" s="39"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A79" s="26" t="s">
         <v>153</v>
       </c>
-      <c r="B79" s="24" t="s">
+      <c r="B79" s="28" t="s">
         <v>154</v>
       </c>
       <c r="C79" s="26" t="s">
@@ -3487,122 +3487,122 @@
       <c r="D79" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="E79" s="24" t="s">
+      <c r="E79" s="28" t="s">
         <v>155</v>
       </c>
-      <c r="F79" s="24" t="s">
+      <c r="F79" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="G79" s="31" t="s">
+      <c r="G79" s="29" t="s">
         <v>160</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="I79" s="31" t="s">
+      <c r="I79" s="29" t="s">
         <v>166</v>
       </c>
-      <c r="J79" s="24" t="s">
+      <c r="J79" s="28" t="s">
         <v>282</v>
       </c>
-      <c r="K79" s="27" t="s">
+      <c r="K79" s="34" t="s">
         <v>280</v>
       </c>
-      <c r="L79" s="29"/>
+      <c r="L79" s="37"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A80" s="26"/>
-      <c r="B80" s="24"/>
+      <c r="B80" s="28"/>
       <c r="C80" s="26"/>
       <c r="D80" s="26"/>
-      <c r="E80" s="24"/>
-      <c r="F80" s="25"/>
-      <c r="G80" s="33"/>
+      <c r="E80" s="28"/>
+      <c r="F80" s="27"/>
+      <c r="G80" s="44"/>
       <c r="H80" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="I80" s="32"/>
-      <c r="J80" s="25"/>
-      <c r="K80" s="28"/>
-      <c r="L80" s="30"/>
+      <c r="I80" s="30"/>
+      <c r="J80" s="27"/>
+      <c r="K80" s="35"/>
+      <c r="L80" s="38"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81" s="26"/>
-      <c r="B81" s="24"/>
+      <c r="B81" s="28"/>
       <c r="C81" s="26"/>
       <c r="D81" s="26"/>
-      <c r="E81" s="24"/>
-      <c r="F81" s="25"/>
-      <c r="G81" s="33"/>
+      <c r="E81" s="28"/>
+      <c r="F81" s="27"/>
+      <c r="G81" s="44"/>
       <c r="H81" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="I81" s="32"/>
-      <c r="J81" s="25"/>
-      <c r="K81" s="28"/>
-      <c r="L81" s="30"/>
+      <c r="I81" s="30"/>
+      <c r="J81" s="27"/>
+      <c r="K81" s="35"/>
+      <c r="L81" s="38"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82" s="26"/>
-      <c r="B82" s="24"/>
+      <c r="B82" s="28"/>
       <c r="C82" s="26"/>
       <c r="D82" s="26"/>
-      <c r="E82" s="24"/>
-      <c r="F82" s="25"/>
-      <c r="G82" s="33"/>
+      <c r="E82" s="28"/>
+      <c r="F82" s="27"/>
+      <c r="G82" s="44"/>
       <c r="H82" s="3"/>
-      <c r="I82" s="32"/>
-      <c r="J82" s="25"/>
-      <c r="K82" s="28"/>
-      <c r="L82" s="30"/>
+      <c r="I82" s="30"/>
+      <c r="J82" s="27"/>
+      <c r="K82" s="35"/>
+      <c r="L82" s="38"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A83" s="26"/>
-      <c r="B83" s="24"/>
+      <c r="B83" s="28"/>
       <c r="C83" s="26"/>
       <c r="D83" s="26"/>
-      <c r="E83" s="24"/>
-      <c r="F83" s="25"/>
-      <c r="G83" s="33"/>
+      <c r="E83" s="28"/>
+      <c r="F83" s="27"/>
+      <c r="G83" s="44"/>
       <c r="H83" s="3"/>
-      <c r="I83" s="32"/>
-      <c r="J83" s="25"/>
-      <c r="K83" s="28"/>
-      <c r="L83" s="30"/>
+      <c r="I83" s="30"/>
+      <c r="J83" s="27"/>
+      <c r="K83" s="35"/>
+      <c r="L83" s="38"/>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84" s="26"/>
-      <c r="B84" s="24"/>
+      <c r="B84" s="28"/>
       <c r="C84" s="26"/>
       <c r="D84" s="26"/>
-      <c r="E84" s="24"/>
-      <c r="F84" s="25"/>
-      <c r="G84" s="33"/>
+      <c r="E84" s="28"/>
+      <c r="F84" s="27"/>
+      <c r="G84" s="44"/>
       <c r="H84" s="3"/>
-      <c r="I84" s="32"/>
-      <c r="J84" s="25"/>
-      <c r="K84" s="28"/>
-      <c r="L84" s="30"/>
+      <c r="I84" s="30"/>
+      <c r="J84" s="27"/>
+      <c r="K84" s="35"/>
+      <c r="L84" s="38"/>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A85" s="26"/>
-      <c r="B85" s="24"/>
+      <c r="B85" s="28"/>
       <c r="C85" s="26"/>
       <c r="D85" s="26"/>
-      <c r="E85" s="24"/>
-      <c r="F85" s="25"/>
-      <c r="G85" s="34"/>
+      <c r="E85" s="28"/>
+      <c r="F85" s="27"/>
+      <c r="G85" s="45"/>
       <c r="H85" s="3"/>
-      <c r="I85" s="36"/>
-      <c r="J85" s="25"/>
-      <c r="K85" s="37"/>
-      <c r="L85" s="35"/>
+      <c r="I85" s="31"/>
+      <c r="J85" s="27"/>
+      <c r="K85" s="36"/>
+      <c r="L85" s="39"/>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A86" s="26" t="s">
         <v>161</v>
       </c>
-      <c r="B86" s="24" t="s">
+      <c r="B86" s="28" t="s">
         <v>162</v>
       </c>
       <c r="C86" s="26" t="s">
@@ -3611,122 +3611,122 @@
       <c r="D86" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="E86" s="24" t="s">
+      <c r="E86" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="F86" s="24" t="s">
+      <c r="F86" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="G86" s="31" t="s">
+      <c r="G86" s="29" t="s">
         <v>167</v>
       </c>
       <c r="H86" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="I86" s="31" t="s">
+      <c r="I86" s="29" t="s">
         <v>169</v>
       </c>
-      <c r="J86" s="24" t="s">
+      <c r="J86" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="K86" s="27" t="s">
+      <c r="K86" s="34" t="s">
         <v>280</v>
       </c>
-      <c r="L86" s="29"/>
+      <c r="L86" s="37"/>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A87" s="26"/>
-      <c r="B87" s="24"/>
+      <c r="B87" s="28"/>
       <c r="C87" s="26"/>
       <c r="D87" s="26"/>
-      <c r="E87" s="24"/>
-      <c r="F87" s="25"/>
-      <c r="G87" s="33"/>
+      <c r="E87" s="28"/>
+      <c r="F87" s="27"/>
+      <c r="G87" s="44"/>
       <c r="H87" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="I87" s="32"/>
-      <c r="J87" s="25"/>
-      <c r="K87" s="28"/>
-      <c r="L87" s="30"/>
+      <c r="I87" s="30"/>
+      <c r="J87" s="27"/>
+      <c r="K87" s="35"/>
+      <c r="L87" s="38"/>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A88" s="26"/>
-      <c r="B88" s="24"/>
+      <c r="B88" s="28"/>
       <c r="C88" s="26"/>
       <c r="D88" s="26"/>
-      <c r="E88" s="24"/>
-      <c r="F88" s="25"/>
-      <c r="G88" s="33"/>
+      <c r="E88" s="28"/>
+      <c r="F88" s="27"/>
+      <c r="G88" s="44"/>
       <c r="H88" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="I88" s="32"/>
-      <c r="J88" s="25"/>
-      <c r="K88" s="28"/>
-      <c r="L88" s="30"/>
+      <c r="I88" s="30"/>
+      <c r="J88" s="27"/>
+      <c r="K88" s="35"/>
+      <c r="L88" s="38"/>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A89" s="26"/>
-      <c r="B89" s="24"/>
+      <c r="B89" s="28"/>
       <c r="C89" s="26"/>
       <c r="D89" s="26"/>
-      <c r="E89" s="24"/>
-      <c r="F89" s="25"/>
-      <c r="G89" s="33"/>
+      <c r="E89" s="28"/>
+      <c r="F89" s="27"/>
+      <c r="G89" s="44"/>
       <c r="H89" s="3"/>
-      <c r="I89" s="32"/>
-      <c r="J89" s="25"/>
-      <c r="K89" s="28"/>
-      <c r="L89" s="30"/>
+      <c r="I89" s="30"/>
+      <c r="J89" s="27"/>
+      <c r="K89" s="35"/>
+      <c r="L89" s="38"/>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A90" s="26"/>
-      <c r="B90" s="24"/>
+      <c r="B90" s="28"/>
       <c r="C90" s="26"/>
       <c r="D90" s="26"/>
-      <c r="E90" s="24"/>
-      <c r="F90" s="25"/>
-      <c r="G90" s="33"/>
+      <c r="E90" s="28"/>
+      <c r="F90" s="27"/>
+      <c r="G90" s="44"/>
       <c r="H90" s="3"/>
-      <c r="I90" s="32"/>
-      <c r="J90" s="25"/>
-      <c r="K90" s="28"/>
-      <c r="L90" s="30"/>
+      <c r="I90" s="30"/>
+      <c r="J90" s="27"/>
+      <c r="K90" s="35"/>
+      <c r="L90" s="38"/>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A91" s="26"/>
-      <c r="B91" s="24"/>
+      <c r="B91" s="28"/>
       <c r="C91" s="26"/>
       <c r="D91" s="26"/>
-      <c r="E91" s="24"/>
-      <c r="F91" s="25"/>
-      <c r="G91" s="33"/>
+      <c r="E91" s="28"/>
+      <c r="F91" s="27"/>
+      <c r="G91" s="44"/>
       <c r="H91" s="3"/>
-      <c r="I91" s="32"/>
-      <c r="J91" s="25"/>
-      <c r="K91" s="28"/>
-      <c r="L91" s="30"/>
+      <c r="I91" s="30"/>
+      <c r="J91" s="27"/>
+      <c r="K91" s="35"/>
+      <c r="L91" s="38"/>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A92" s="26"/>
-      <c r="B92" s="24"/>
+      <c r="B92" s="28"/>
       <c r="C92" s="26"/>
       <c r="D92" s="26"/>
-      <c r="E92" s="24"/>
-      <c r="F92" s="25"/>
-      <c r="G92" s="34"/>
+      <c r="E92" s="28"/>
+      <c r="F92" s="27"/>
+      <c r="G92" s="45"/>
       <c r="H92" s="3"/>
-      <c r="I92" s="36"/>
-      <c r="J92" s="25"/>
-      <c r="K92" s="37"/>
-      <c r="L92" s="35"/>
+      <c r="I92" s="31"/>
+      <c r="J92" s="27"/>
+      <c r="K92" s="36"/>
+      <c r="L92" s="39"/>
     </row>
     <row r="93" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="B93" s="24" t="s">
+      <c r="B93" s="28" t="s">
         <v>168</v>
       </c>
       <c r="C93" s="26" t="s">
@@ -3735,114 +3735,114 @@
       <c r="D93" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="E93" s="24" t="s">
+      <c r="E93" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="F93" s="24" t="s">
+      <c r="F93" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="G93" s="31" t="s">
+      <c r="G93" s="29" t="s">
         <v>176</v>
       </c>
       <c r="H93" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="I93" s="24" t="s">
+      <c r="I93" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="J93" s="24" t="s">
+      <c r="J93" s="28" t="s">
         <v>283</v>
       </c>
       <c r="K93" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="L93" s="23"/>
+      <c r="L93" s="46"/>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A94" s="26"/>
-      <c r="B94" s="24"/>
+      <c r="B94" s="28"/>
       <c r="C94" s="26"/>
       <c r="D94" s="26"/>
-      <c r="E94" s="24"/>
-      <c r="F94" s="25"/>
-      <c r="G94" s="33"/>
+      <c r="E94" s="28"/>
+      <c r="F94" s="27"/>
+      <c r="G94" s="44"/>
       <c r="H94" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="I94" s="25"/>
-      <c r="J94" s="25"/>
+      <c r="I94" s="27"/>
+      <c r="J94" s="27"/>
       <c r="K94" s="26"/>
-      <c r="L94" s="23"/>
+      <c r="L94" s="46"/>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A95" s="26"/>
-      <c r="B95" s="24"/>
+      <c r="B95" s="28"/>
       <c r="C95" s="26"/>
       <c r="D95" s="26"/>
-      <c r="E95" s="24"/>
-      <c r="F95" s="25"/>
-      <c r="G95" s="33"/>
+      <c r="E95" s="28"/>
+      <c r="F95" s="27"/>
+      <c r="G95" s="44"/>
       <c r="H95" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="I95" s="25"/>
-      <c r="J95" s="25"/>
+      <c r="I95" s="27"/>
+      <c r="J95" s="27"/>
       <c r="K95" s="26"/>
-      <c r="L95" s="23"/>
+      <c r="L95" s="46"/>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96" s="26"/>
-      <c r="B96" s="24"/>
+      <c r="B96" s="28"/>
       <c r="C96" s="26"/>
       <c r="D96" s="26"/>
-      <c r="E96" s="24"/>
-      <c r="F96" s="25"/>
-      <c r="G96" s="33"/>
+      <c r="E96" s="28"/>
+      <c r="F96" s="27"/>
+      <c r="G96" s="44"/>
       <c r="H96" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="I96" s="25"/>
-      <c r="J96" s="25"/>
+      <c r="I96" s="27"/>
+      <c r="J96" s="27"/>
       <c r="K96" s="26"/>
-      <c r="L96" s="23"/>
+      <c r="L96" s="46"/>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A97" s="26"/>
-      <c r="B97" s="24"/>
+      <c r="B97" s="28"/>
       <c r="C97" s="26"/>
       <c r="D97" s="26"/>
-      <c r="E97" s="24"/>
-      <c r="F97" s="25"/>
-      <c r="G97" s="33"/>
+      <c r="E97" s="28"/>
+      <c r="F97" s="27"/>
+      <c r="G97" s="44"/>
       <c r="H97" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="I97" s="25"/>
-      <c r="J97" s="25"/>
+      <c r="I97" s="27"/>
+      <c r="J97" s="27"/>
       <c r="K97" s="26"/>
-      <c r="L97" s="23"/>
+      <c r="L97" s="46"/>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A98" s="26"/>
-      <c r="B98" s="24"/>
+      <c r="B98" s="28"/>
       <c r="C98" s="26"/>
       <c r="D98" s="26"/>
-      <c r="E98" s="24"/>
-      <c r="F98" s="25"/>
-      <c r="G98" s="34"/>
+      <c r="E98" s="28"/>
+      <c r="F98" s="27"/>
+      <c r="G98" s="45"/>
       <c r="H98" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="I98" s="25"/>
-      <c r="J98" s="25"/>
+      <c r="I98" s="27"/>
+      <c r="J98" s="27"/>
       <c r="K98" s="26"/>
-      <c r="L98" s="23"/>
+      <c r="L98" s="46"/>
     </row>
     <row r="99" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="B99" s="24" t="s">
+      <c r="B99" s="28" t="s">
         <v>179</v>
       </c>
       <c r="C99" s="26" t="s">
@@ -3851,130 +3851,130 @@
       <c r="D99" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="E99" s="24" t="s">
+      <c r="E99" s="28" t="s">
         <v>189</v>
       </c>
-      <c r="F99" s="24" t="s">
+      <c r="F99" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="G99" s="31" t="s">
+      <c r="G99" s="29" t="s">
         <v>180</v>
       </c>
       <c r="H99" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="I99" s="24" t="s">
+      <c r="I99" s="28" t="s">
         <v>186</v>
       </c>
-      <c r="J99" s="24" t="s">
+      <c r="J99" s="28" t="s">
         <v>186</v>
       </c>
       <c r="K99" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="L99" s="23"/>
+      <c r="L99" s="46"/>
     </row>
     <row r="100" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="26"/>
-      <c r="B100" s="24"/>
+      <c r="B100" s="28"/>
       <c r="C100" s="26"/>
       <c r="D100" s="26"/>
-      <c r="E100" s="24"/>
-      <c r="F100" s="25"/>
-      <c r="G100" s="33"/>
+      <c r="E100" s="28"/>
+      <c r="F100" s="27"/>
+      <c r="G100" s="44"/>
       <c r="H100" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="I100" s="25"/>
-      <c r="J100" s="25"/>
+      <c r="I100" s="27"/>
+      <c r="J100" s="27"/>
       <c r="K100" s="26"/>
-      <c r="L100" s="23"/>
+      <c r="L100" s="46"/>
     </row>
     <row r="101" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="26"/>
-      <c r="B101" s="24"/>
+      <c r="B101" s="28"/>
       <c r="C101" s="26"/>
       <c r="D101" s="26"/>
-      <c r="E101" s="24"/>
-      <c r="F101" s="25"/>
-      <c r="G101" s="33"/>
+      <c r="E101" s="28"/>
+      <c r="F101" s="27"/>
+      <c r="G101" s="44"/>
       <c r="H101" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="I101" s="25"/>
-      <c r="J101" s="25"/>
+      <c r="I101" s="27"/>
+      <c r="J101" s="27"/>
       <c r="K101" s="26"/>
-      <c r="L101" s="23"/>
+      <c r="L101" s="46"/>
     </row>
     <row r="102" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="26"/>
-      <c r="B102" s="24"/>
+      <c r="B102" s="28"/>
       <c r="C102" s="26"/>
       <c r="D102" s="26"/>
-      <c r="E102" s="24"/>
-      <c r="F102" s="25"/>
-      <c r="G102" s="33"/>
+      <c r="E102" s="28"/>
+      <c r="F102" s="27"/>
+      <c r="G102" s="44"/>
       <c r="H102" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="I102" s="25"/>
-      <c r="J102" s="25"/>
+      <c r="I102" s="27"/>
+      <c r="J102" s="27"/>
       <c r="K102" s="26"/>
-      <c r="L102" s="23"/>
+      <c r="L102" s="46"/>
     </row>
     <row r="103" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="26"/>
-      <c r="B103" s="24"/>
+      <c r="B103" s="28"/>
       <c r="C103" s="26"/>
       <c r="D103" s="26"/>
-      <c r="E103" s="24"/>
-      <c r="F103" s="25"/>
-      <c r="G103" s="33"/>
+      <c r="E103" s="28"/>
+      <c r="F103" s="27"/>
+      <c r="G103" s="44"/>
       <c r="H103" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="I103" s="25"/>
-      <c r="J103" s="25"/>
+      <c r="I103" s="27"/>
+      <c r="J103" s="27"/>
       <c r="K103" s="26"/>
-      <c r="L103" s="23"/>
+      <c r="L103" s="46"/>
     </row>
     <row r="104" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="26"/>
-      <c r="B104" s="24"/>
+      <c r="B104" s="28"/>
       <c r="C104" s="26"/>
       <c r="D104" s="26"/>
-      <c r="E104" s="24"/>
-      <c r="F104" s="25"/>
-      <c r="G104" s="33"/>
+      <c r="E104" s="28"/>
+      <c r="F104" s="27"/>
+      <c r="G104" s="44"/>
       <c r="H104" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="I104" s="25"/>
-      <c r="J104" s="25"/>
+      <c r="I104" s="27"/>
+      <c r="J104" s="27"/>
       <c r="K104" s="26"/>
-      <c r="L104" s="23"/>
+      <c r="L104" s="46"/>
     </row>
     <row r="105" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="26"/>
-      <c r="B105" s="24"/>
+      <c r="B105" s="28"/>
       <c r="C105" s="26"/>
       <c r="D105" s="26"/>
-      <c r="E105" s="24"/>
-      <c r="F105" s="25"/>
-      <c r="G105" s="34"/>
+      <c r="E105" s="28"/>
+      <c r="F105" s="27"/>
+      <c r="G105" s="45"/>
       <c r="H105" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="I105" s="25"/>
-      <c r="J105" s="25"/>
+      <c r="I105" s="27"/>
+      <c r="J105" s="27"/>
       <c r="K105" s="26"/>
-      <c r="L105" s="23"/>
+      <c r="L105" s="46"/>
     </row>
     <row r="106" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="B106" s="24" t="s">
+      <c r="B106" s="28" t="s">
         <v>188</v>
       </c>
       <c r="C106" s="26" t="s">
@@ -3983,22 +3983,22 @@
       <c r="D106" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="E106" s="24" t="s">
+      <c r="E106" s="28" t="s">
         <v>190</v>
       </c>
-      <c r="F106" s="24" t="s">
+      <c r="F106" s="28" t="s">
         <v>191</v>
       </c>
-      <c r="G106" s="31" t="s">
+      <c r="G106" s="29" t="s">
         <v>198</v>
       </c>
       <c r="H106" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="I106" s="24" t="s">
+      <c r="I106" s="28" t="s">
         <v>197</v>
       </c>
-      <c r="J106" s="24" t="s">
+      <c r="J106" s="28" t="s">
         <v>197</v>
       </c>
       <c r="K106" s="26" t="s">
@@ -4007,105 +4007,105 @@
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A107" s="26"/>
-      <c r="B107" s="24"/>
+      <c r="B107" s="28"/>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="24"/>
-      <c r="F107" s="25"/>
-      <c r="G107" s="33"/>
+      <c r="E107" s="28"/>
+      <c r="F107" s="27"/>
+      <c r="G107" s="44"/>
       <c r="H107" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="I107" s="25"/>
-      <c r="J107" s="25"/>
+      <c r="I107" s="27"/>
+      <c r="J107" s="27"/>
       <c r="K107" s="26"/>
-      <c r="L107" s="45"/>
+      <c r="L107" s="23"/>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A108" s="26"/>
-      <c r="B108" s="24"/>
+      <c r="B108" s="28"/>
       <c r="C108" s="26"/>
       <c r="D108" s="26"/>
-      <c r="E108" s="24"/>
-      <c r="F108" s="25"/>
-      <c r="G108" s="33"/>
+      <c r="E108" s="28"/>
+      <c r="F108" s="27"/>
+      <c r="G108" s="44"/>
       <c r="H108" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="I108" s="25"/>
-      <c r="J108" s="25"/>
+      <c r="I108" s="27"/>
+      <c r="J108" s="27"/>
       <c r="K108" s="26"/>
       <c r="M108" s="22"/>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A109" s="26"/>
-      <c r="B109" s="24"/>
+      <c r="B109" s="28"/>
       <c r="C109" s="26"/>
       <c r="D109" s="26"/>
-      <c r="E109" s="24"/>
-      <c r="F109" s="25"/>
-      <c r="G109" s="33"/>
+      <c r="E109" s="28"/>
+      <c r="F109" s="27"/>
+      <c r="G109" s="44"/>
       <c r="H109" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="I109" s="25"/>
-      <c r="J109" s="25"/>
+      <c r="I109" s="27"/>
+      <c r="J109" s="27"/>
       <c r="K109" s="26"/>
-      <c r="L109" s="45"/>
-      <c r="M109" s="45"/>
+      <c r="L109" s="23"/>
+      <c r="M109" s="23"/>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A110" s="26"/>
-      <c r="B110" s="24"/>
+      <c r="B110" s="28"/>
       <c r="C110" s="26"/>
       <c r="D110" s="26"/>
-      <c r="E110" s="24"/>
-      <c r="F110" s="25"/>
-      <c r="G110" s="33"/>
+      <c r="E110" s="28"/>
+      <c r="F110" s="27"/>
+      <c r="G110" s="44"/>
       <c r="H110" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="I110" s="25"/>
-      <c r="J110" s="25"/>
+      <c r="I110" s="27"/>
+      <c r="J110" s="27"/>
       <c r="K110" s="26"/>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A111" s="26"/>
-      <c r="B111" s="24"/>
+      <c r="B111" s="28"/>
       <c r="C111" s="26"/>
       <c r="D111" s="26"/>
-      <c r="E111" s="24"/>
-      <c r="F111" s="25"/>
-      <c r="G111" s="33"/>
+      <c r="E111" s="28"/>
+      <c r="F111" s="27"/>
+      <c r="G111" s="44"/>
       <c r="H111" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="I111" s="25"/>
-      <c r="J111" s="25"/>
+      <c r="I111" s="27"/>
+      <c r="J111" s="27"/>
       <c r="K111" s="26"/>
-      <c r="L111" s="45"/>
+      <c r="L111" s="23"/>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A112" s="26"/>
-      <c r="B112" s="24"/>
+      <c r="B112" s="28"/>
       <c r="C112" s="26"/>
       <c r="D112" s="26"/>
-      <c r="E112" s="24"/>
-      <c r="F112" s="25"/>
-      <c r="G112" s="34"/>
+      <c r="E112" s="28"/>
+      <c r="F112" s="27"/>
+      <c r="G112" s="45"/>
       <c r="H112" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="I112" s="25"/>
-      <c r="J112" s="25"/>
+      <c r="I112" s="27"/>
+      <c r="J112" s="27"/>
       <c r="K112" s="26"/>
-      <c r="L112" s="45"/>
+      <c r="L112" s="23"/>
     </row>
     <row r="113" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="26" t="s">
         <v>199</v>
       </c>
-      <c r="B113" s="24" t="s">
+      <c r="B113" s="28" t="s">
         <v>200</v>
       </c>
       <c r="C113" s="26" t="s">
@@ -4114,132 +4114,132 @@
       <c r="D113" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="E113" s="24" t="s">
+      <c r="E113" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="F113" s="24" t="s">
+      <c r="F113" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="G113" s="31" t="s">
+      <c r="G113" s="29" t="s">
         <v>203</v>
       </c>
       <c r="H113" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="I113" s="24" t="s">
+      <c r="I113" s="28" t="s">
         <v>286</v>
       </c>
-      <c r="J113" s="24" t="s">
+      <c r="J113" s="28" t="s">
         <v>285</v>
       </c>
       <c r="K113" s="26" t="s">
         <v>284</v>
       </c>
-      <c r="L113" s="24" t="s">
+      <c r="L113" s="28" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A114" s="26"/>
-      <c r="B114" s="24"/>
+      <c r="B114" s="28"/>
       <c r="C114" s="26"/>
       <c r="D114" s="26"/>
-      <c r="E114" s="24"/>
-      <c r="F114" s="25"/>
-      <c r="G114" s="33"/>
+      <c r="E114" s="28"/>
+      <c r="F114" s="27"/>
+      <c r="G114" s="44"/>
       <c r="H114" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="I114" s="25"/>
-      <c r="J114" s="25"/>
+      <c r="I114" s="27"/>
+      <c r="J114" s="27"/>
       <c r="K114" s="26"/>
-      <c r="L114" s="25"/>
+      <c r="L114" s="27"/>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A115" s="26"/>
-      <c r="B115" s="24"/>
+      <c r="B115" s="28"/>
       <c r="C115" s="26"/>
       <c r="D115" s="26"/>
-      <c r="E115" s="24"/>
-      <c r="F115" s="25"/>
-      <c r="G115" s="33"/>
+      <c r="E115" s="28"/>
+      <c r="F115" s="27"/>
+      <c r="G115" s="44"/>
       <c r="H115" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="I115" s="25"/>
-      <c r="J115" s="25"/>
+      <c r="I115" s="27"/>
+      <c r="J115" s="27"/>
       <c r="K115" s="26"/>
-      <c r="L115" s="25"/>
+      <c r="L115" s="27"/>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A116" s="26"/>
-      <c r="B116" s="24"/>
+      <c r="B116" s="28"/>
       <c r="C116" s="26"/>
       <c r="D116" s="26"/>
-      <c r="E116" s="24"/>
-      <c r="F116" s="25"/>
-      <c r="G116" s="33"/>
+      <c r="E116" s="28"/>
+      <c r="F116" s="27"/>
+      <c r="G116" s="44"/>
       <c r="H116" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="I116" s="25"/>
-      <c r="J116" s="25"/>
+      <c r="I116" s="27"/>
+      <c r="J116" s="27"/>
       <c r="K116" s="26"/>
-      <c r="L116" s="25"/>
+      <c r="L116" s="27"/>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A117" s="26"/>
-      <c r="B117" s="24"/>
+      <c r="B117" s="28"/>
       <c r="C117" s="26"/>
       <c r="D117" s="26"/>
-      <c r="E117" s="24"/>
-      <c r="F117" s="25"/>
-      <c r="G117" s="33"/>
+      <c r="E117" s="28"/>
+      <c r="F117" s="27"/>
+      <c r="G117" s="44"/>
       <c r="H117" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="I117" s="25"/>
-      <c r="J117" s="25"/>
+      <c r="I117" s="27"/>
+      <c r="J117" s="27"/>
       <c r="K117" s="26"/>
-      <c r="L117" s="25"/>
+      <c r="L117" s="27"/>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A118" s="26"/>
-      <c r="B118" s="24"/>
+      <c r="B118" s="28"/>
       <c r="C118" s="26"/>
       <c r="D118" s="26"/>
-      <c r="E118" s="24"/>
-      <c r="F118" s="25"/>
-      <c r="G118" s="33"/>
+      <c r="E118" s="28"/>
+      <c r="F118" s="27"/>
+      <c r="G118" s="44"/>
       <c r="H118" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="I118" s="25"/>
-      <c r="J118" s="25"/>
+      <c r="I118" s="27"/>
+      <c r="J118" s="27"/>
       <c r="K118" s="26"/>
-      <c r="L118" s="25"/>
+      <c r="L118" s="27"/>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A119" s="26"/>
-      <c r="B119" s="24"/>
+      <c r="B119" s="28"/>
       <c r="C119" s="26"/>
       <c r="D119" s="26"/>
-      <c r="E119" s="24"/>
-      <c r="F119" s="25"/>
-      <c r="G119" s="34"/>
+      <c r="E119" s="28"/>
+      <c r="F119" s="27"/>
+      <c r="G119" s="45"/>
       <c r="H119" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="I119" s="25"/>
-      <c r="J119" s="25"/>
+      <c r="I119" s="27"/>
+      <c r="J119" s="27"/>
       <c r="K119" s="26"/>
-      <c r="L119" s="25"/>
+      <c r="L119" s="27"/>
     </row>
     <row r="120" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="26" t="s">
         <v>207</v>
       </c>
-      <c r="B120" s="24" t="s">
+      <c r="B120" s="28" t="s">
         <v>208</v>
       </c>
       <c r="C120" s="26" t="s">
@@ -4248,66 +4248,66 @@
       <c r="D120" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="E120" s="24" t="s">
+      <c r="E120" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="F120" s="24" t="s">
+      <c r="F120" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G120" s="31" t="s">
+      <c r="G120" s="29" t="s">
         <v>211</v>
       </c>
       <c r="H120" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="I120" s="24" t="s">
+      <c r="I120" s="28" t="s">
         <v>213</v>
       </c>
-      <c r="J120" s="24" t="s">
+      <c r="J120" s="28" t="s">
         <v>213</v>
       </c>
       <c r="K120" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="L120" s="23"/>
+      <c r="L120" s="46"/>
     </row>
     <row r="121" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="26"/>
-      <c r="B121" s="24"/>
+      <c r="B121" s="28"/>
       <c r="C121" s="26"/>
       <c r="D121" s="26"/>
-      <c r="E121" s="24"/>
-      <c r="F121" s="25"/>
-      <c r="G121" s="33"/>
+      <c r="E121" s="28"/>
+      <c r="F121" s="27"/>
+      <c r="G121" s="44"/>
       <c r="H121" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="I121" s="25"/>
-      <c r="J121" s="25"/>
+      <c r="I121" s="27"/>
+      <c r="J121" s="27"/>
       <c r="K121" s="26"/>
-      <c r="L121" s="23"/>
+      <c r="L121" s="46"/>
     </row>
     <row r="122" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="26"/>
-      <c r="B122" s="24"/>
+      <c r="B122" s="28"/>
       <c r="C122" s="26"/>
       <c r="D122" s="26"/>
-      <c r="E122" s="24"/>
-      <c r="F122" s="25"/>
-      <c r="G122" s="33"/>
+      <c r="E122" s="28"/>
+      <c r="F122" s="27"/>
+      <c r="G122" s="44"/>
       <c r="H122" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="I122" s="25"/>
-      <c r="J122" s="25"/>
+      <c r="I122" s="27"/>
+      <c r="J122" s="27"/>
       <c r="K122" s="26"/>
-      <c r="L122" s="23"/>
+      <c r="L122" s="46"/>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A123" s="26" t="s">
         <v>248</v>
       </c>
-      <c r="B123" s="24" t="s">
+      <c r="B123" s="28" t="s">
         <v>214</v>
       </c>
       <c r="C123" s="26" t="s">
@@ -4316,82 +4316,82 @@
       <c r="D123" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="E123" s="24" t="s">
+      <c r="E123" s="28" t="s">
         <v>228</v>
       </c>
-      <c r="F123" s="24" t="s">
+      <c r="F123" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="G123" s="24" t="s">
+      <c r="G123" s="28" t="s">
         <v>230</v>
       </c>
       <c r="H123" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="I123" s="24" t="s">
+      <c r="I123" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="J123" s="44" t="s">
+      <c r="J123" s="47" t="s">
         <v>235</v>
       </c>
       <c r="K123" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="L123" s="23"/>
+      <c r="L123" s="46"/>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A124" s="26"/>
-      <c r="B124" s="24"/>
+      <c r="B124" s="28"/>
       <c r="C124" s="26"/>
       <c r="D124" s="26"/>
-      <c r="E124" s="24"/>
-      <c r="F124" s="25"/>
-      <c r="G124" s="25"/>
+      <c r="E124" s="28"/>
+      <c r="F124" s="27"/>
+      <c r="G124" s="27"/>
       <c r="H124" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="I124" s="25"/>
-      <c r="J124" s="23"/>
+      <c r="I124" s="27"/>
+      <c r="J124" s="46"/>
       <c r="K124" s="26"/>
-      <c r="L124" s="23"/>
+      <c r="L124" s="46"/>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A125" s="26"/>
-      <c r="B125" s="24"/>
+      <c r="B125" s="28"/>
       <c r="C125" s="26"/>
       <c r="D125" s="26"/>
-      <c r="E125" s="24"/>
-      <c r="F125" s="25"/>
-      <c r="G125" s="25"/>
+      <c r="E125" s="28"/>
+      <c r="F125" s="27"/>
+      <c r="G125" s="27"/>
       <c r="H125" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="I125" s="25"/>
-      <c r="J125" s="23"/>
+      <c r="I125" s="27"/>
+      <c r="J125" s="46"/>
       <c r="K125" s="26"/>
-      <c r="L125" s="23"/>
+      <c r="L125" s="46"/>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A126" s="26"/>
-      <c r="B126" s="24"/>
+      <c r="B126" s="28"/>
       <c r="C126" s="26"/>
       <c r="D126" s="26"/>
-      <c r="E126" s="24"/>
-      <c r="F126" s="25"/>
-      <c r="G126" s="25"/>
+      <c r="E126" s="28"/>
+      <c r="F126" s="27"/>
+      <c r="G126" s="27"/>
       <c r="H126" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I126" s="25"/>
-      <c r="J126" s="23"/>
+      <c r="I126" s="27"/>
+      <c r="J126" s="46"/>
       <c r="K126" s="26"/>
-      <c r="L126" s="23"/>
+      <c r="L126" s="46"/>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A127" s="26" t="s">
         <v>247</v>
       </c>
-      <c r="B127" s="24" t="s">
+      <c r="B127" s="28" t="s">
         <v>236</v>
       </c>
       <c r="C127" s="26" t="s">
@@ -4400,114 +4400,114 @@
       <c r="D127" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="E127" s="24" t="s">
+      <c r="E127" s="28" t="s">
         <v>237</v>
       </c>
-      <c r="F127" s="24" t="s">
+      <c r="F127" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="G127" s="24" t="s">
+      <c r="G127" s="28" t="s">
         <v>238</v>
       </c>
       <c r="H127" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="I127" s="24" t="s">
+      <c r="I127" s="28" t="s">
         <v>245</v>
       </c>
-      <c r="J127" s="24" t="s">
+      <c r="J127" s="28" t="s">
         <v>245</v>
       </c>
       <c r="K127" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="L127" s="23"/>
+      <c r="L127" s="46"/>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A128" s="26"/>
-      <c r="B128" s="24"/>
+      <c r="B128" s="28"/>
       <c r="C128" s="26"/>
       <c r="D128" s="26"/>
-      <c r="E128" s="24"/>
-      <c r="F128" s="25"/>
-      <c r="G128" s="25"/>
+      <c r="E128" s="28"/>
+      <c r="F128" s="27"/>
+      <c r="G128" s="27"/>
       <c r="H128" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="I128" s="25"/>
-      <c r="J128" s="25"/>
+      <c r="I128" s="27"/>
+      <c r="J128" s="27"/>
       <c r="K128" s="26"/>
-      <c r="L128" s="23"/>
+      <c r="L128" s="46"/>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A129" s="26"/>
-      <c r="B129" s="24"/>
+      <c r="B129" s="28"/>
       <c r="C129" s="26"/>
       <c r="D129" s="26"/>
-      <c r="E129" s="24"/>
-      <c r="F129" s="25"/>
-      <c r="G129" s="25"/>
+      <c r="E129" s="28"/>
+      <c r="F129" s="27"/>
+      <c r="G129" s="27"/>
       <c r="H129" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="I129" s="25"/>
-      <c r="J129" s="25"/>
+      <c r="I129" s="27"/>
+      <c r="J129" s="27"/>
       <c r="K129" s="26"/>
-      <c r="L129" s="23"/>
+      <c r="L129" s="46"/>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A130" s="26"/>
-      <c r="B130" s="24"/>
+      <c r="B130" s="28"/>
       <c r="C130" s="26"/>
       <c r="D130" s="26"/>
-      <c r="E130" s="24"/>
-      <c r="F130" s="25"/>
-      <c r="G130" s="25"/>
+      <c r="E130" s="28"/>
+      <c r="F130" s="27"/>
+      <c r="G130" s="27"/>
       <c r="H130" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="I130" s="25"/>
-      <c r="J130" s="25"/>
+      <c r="I130" s="27"/>
+      <c r="J130" s="27"/>
       <c r="K130" s="26"/>
-      <c r="L130" s="23"/>
+      <c r="L130" s="46"/>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A131" s="26"/>
-      <c r="B131" s="24"/>
+      <c r="B131" s="28"/>
       <c r="C131" s="26"/>
       <c r="D131" s="26"/>
-      <c r="E131" s="24"/>
-      <c r="F131" s="25"/>
-      <c r="G131" s="25"/>
+      <c r="E131" s="28"/>
+      <c r="F131" s="27"/>
+      <c r="G131" s="27"/>
       <c r="H131" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="I131" s="25"/>
-      <c r="J131" s="25"/>
+      <c r="I131" s="27"/>
+      <c r="J131" s="27"/>
       <c r="K131" s="26"/>
-      <c r="L131" s="23"/>
+      <c r="L131" s="46"/>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A132" s="26"/>
-      <c r="B132" s="24"/>
+      <c r="B132" s="28"/>
       <c r="C132" s="26"/>
       <c r="D132" s="26"/>
-      <c r="E132" s="24"/>
-      <c r="F132" s="25"/>
-      <c r="G132" s="25"/>
+      <c r="E132" s="28"/>
+      <c r="F132" s="27"/>
+      <c r="G132" s="27"/>
       <c r="H132" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="I132" s="25"/>
-      <c r="J132" s="25"/>
+      <c r="I132" s="27"/>
+      <c r="J132" s="27"/>
       <c r="K132" s="26"/>
-      <c r="L132" s="23"/>
+      <c r="L132" s="46"/>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A133" s="26" t="s">
         <v>246</v>
       </c>
-      <c r="B133" s="24" t="s">
+      <c r="B133" s="28" t="s">
         <v>249</v>
       </c>
       <c r="C133" s="26" t="s">
@@ -4516,146 +4516,146 @@
       <c r="D133" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="E133" s="24" t="s">
+      <c r="E133" s="28" t="s">
         <v>250</v>
       </c>
-      <c r="F133" s="24" t="s">
+      <c r="F133" s="28" t="s">
         <v>251</v>
       </c>
-      <c r="G133" s="24" t="s">
+      <c r="G133" s="28" t="s">
         <v>252</v>
       </c>
       <c r="H133" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="I133" s="24" t="s">
+      <c r="I133" s="28" t="s">
         <v>260</v>
       </c>
-      <c r="J133" s="24" t="s">
+      <c r="J133" s="28" t="s">
         <v>260</v>
       </c>
       <c r="K133" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="L133" s="23"/>
+      <c r="L133" s="46"/>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A134" s="26"/>
-      <c r="B134" s="24"/>
+      <c r="B134" s="28"/>
       <c r="C134" s="26"/>
       <c r="D134" s="26"/>
-      <c r="E134" s="24"/>
-      <c r="F134" s="25"/>
-      <c r="G134" s="25"/>
+      <c r="E134" s="28"/>
+      <c r="F134" s="27"/>
+      <c r="G134" s="27"/>
       <c r="H134" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="I134" s="25"/>
-      <c r="J134" s="25"/>
+      <c r="I134" s="27"/>
+      <c r="J134" s="27"/>
       <c r="K134" s="26"/>
-      <c r="L134" s="23"/>
+      <c r="L134" s="46"/>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A135" s="26"/>
-      <c r="B135" s="24"/>
+      <c r="B135" s="28"/>
       <c r="C135" s="26"/>
       <c r="D135" s="26"/>
-      <c r="E135" s="24"/>
-      <c r="F135" s="25"/>
-      <c r="G135" s="25"/>
+      <c r="E135" s="28"/>
+      <c r="F135" s="27"/>
+      <c r="G135" s="27"/>
       <c r="H135" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="I135" s="25"/>
-      <c r="J135" s="25"/>
+      <c r="I135" s="27"/>
+      <c r="J135" s="27"/>
       <c r="K135" s="26"/>
-      <c r="L135" s="23"/>
+      <c r="L135" s="46"/>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A136" s="26"/>
-      <c r="B136" s="24"/>
+      <c r="B136" s="28"/>
       <c r="C136" s="26"/>
       <c r="D136" s="26"/>
-      <c r="E136" s="24"/>
-      <c r="F136" s="25"/>
-      <c r="G136" s="25"/>
+      <c r="E136" s="28"/>
+      <c r="F136" s="27"/>
+      <c r="G136" s="27"/>
       <c r="H136" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="I136" s="25"/>
-      <c r="J136" s="25"/>
+      <c r="I136" s="27"/>
+      <c r="J136" s="27"/>
       <c r="K136" s="26"/>
-      <c r="L136" s="23"/>
+      <c r="L136" s="46"/>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A137" s="26"/>
-      <c r="B137" s="24"/>
+      <c r="B137" s="28"/>
       <c r="C137" s="26"/>
       <c r="D137" s="26"/>
-      <c r="E137" s="24"/>
-      <c r="F137" s="25"/>
-      <c r="G137" s="25"/>
+      <c r="E137" s="28"/>
+      <c r="F137" s="27"/>
+      <c r="G137" s="27"/>
       <c r="H137" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="I137" s="25"/>
-      <c r="J137" s="25"/>
+      <c r="I137" s="27"/>
+      <c r="J137" s="27"/>
       <c r="K137" s="26"/>
-      <c r="L137" s="23"/>
+      <c r="L137" s="46"/>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A138" s="26"/>
-      <c r="B138" s="24"/>
+      <c r="B138" s="28"/>
       <c r="C138" s="26"/>
       <c r="D138" s="26"/>
-      <c r="E138" s="24"/>
-      <c r="F138" s="25"/>
-      <c r="G138" s="25"/>
+      <c r="E138" s="28"/>
+      <c r="F138" s="27"/>
+      <c r="G138" s="27"/>
       <c r="H138" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="I138" s="25"/>
-      <c r="J138" s="25"/>
+      <c r="I138" s="27"/>
+      <c r="J138" s="27"/>
       <c r="K138" s="26"/>
-      <c r="L138" s="23"/>
+      <c r="L138" s="46"/>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A139" s="26"/>
-      <c r="B139" s="24"/>
+      <c r="B139" s="28"/>
       <c r="C139" s="26"/>
       <c r="D139" s="26"/>
-      <c r="E139" s="24"/>
-      <c r="F139" s="25"/>
-      <c r="G139" s="25"/>
+      <c r="E139" s="28"/>
+      <c r="F139" s="27"/>
+      <c r="G139" s="27"/>
       <c r="H139" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="I139" s="25"/>
-      <c r="J139" s="25"/>
+      <c r="I139" s="27"/>
+      <c r="J139" s="27"/>
       <c r="K139" s="26"/>
-      <c r="L139" s="23"/>
+      <c r="L139" s="46"/>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A140" s="26"/>
-      <c r="B140" s="24"/>
+      <c r="B140" s="28"/>
       <c r="C140" s="26"/>
       <c r="D140" s="26"/>
-      <c r="E140" s="24"/>
-      <c r="F140" s="25"/>
-      <c r="G140" s="25"/>
+      <c r="E140" s="28"/>
+      <c r="F140" s="27"/>
+      <c r="G140" s="27"/>
       <c r="H140" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="I140" s="25"/>
-      <c r="J140" s="25"/>
+      <c r="I140" s="27"/>
+      <c r="J140" s="27"/>
       <c r="K140" s="26"/>
-      <c r="L140" s="23"/>
+      <c r="L140" s="46"/>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A141" s="26" t="s">
         <v>261</v>
       </c>
-      <c r="B141" s="24" t="s">
+      <c r="B141" s="28" t="s">
         <v>262</v>
       </c>
       <c r="C141" s="26" t="s">
@@ -4664,146 +4664,146 @@
       <c r="D141" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="E141" s="24" t="s">
+      <c r="E141" s="28" t="s">
         <v>263</v>
       </c>
-      <c r="F141" s="24" t="s">
+      <c r="F141" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="G141" s="24" t="s">
+      <c r="G141" s="28" t="s">
         <v>264</v>
       </c>
       <c r="H141" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="I141" s="24" t="s">
+      <c r="I141" s="28" t="s">
         <v>271</v>
       </c>
-      <c r="J141" s="24" t="s">
+      <c r="J141" s="28" t="s">
         <v>271</v>
       </c>
       <c r="K141" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="L141" s="23"/>
+      <c r="L141" s="46"/>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A142" s="26"/>
-      <c r="B142" s="24"/>
+      <c r="B142" s="28"/>
       <c r="C142" s="26"/>
       <c r="D142" s="26"/>
-      <c r="E142" s="24"/>
-      <c r="F142" s="25"/>
-      <c r="G142" s="25"/>
+      <c r="E142" s="28"/>
+      <c r="F142" s="27"/>
+      <c r="G142" s="27"/>
       <c r="H142" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="I142" s="25"/>
-      <c r="J142" s="25"/>
+      <c r="I142" s="27"/>
+      <c r="J142" s="27"/>
       <c r="K142" s="26"/>
-      <c r="L142" s="23"/>
+      <c r="L142" s="46"/>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A143" s="26"/>
-      <c r="B143" s="24"/>
+      <c r="B143" s="28"/>
       <c r="C143" s="26"/>
       <c r="D143" s="26"/>
-      <c r="E143" s="24"/>
-      <c r="F143" s="25"/>
-      <c r="G143" s="25"/>
+      <c r="E143" s="28"/>
+      <c r="F143" s="27"/>
+      <c r="G143" s="27"/>
       <c r="H143" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="I143" s="25"/>
-      <c r="J143" s="25"/>
+      <c r="I143" s="27"/>
+      <c r="J143" s="27"/>
       <c r="K143" s="26"/>
-      <c r="L143" s="23"/>
+      <c r="L143" s="46"/>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A144" s="26"/>
-      <c r="B144" s="24"/>
+      <c r="B144" s="28"/>
       <c r="C144" s="26"/>
       <c r="D144" s="26"/>
-      <c r="E144" s="24"/>
-      <c r="F144" s="25"/>
-      <c r="G144" s="25"/>
+      <c r="E144" s="28"/>
+      <c r="F144" s="27"/>
+      <c r="G144" s="27"/>
       <c r="H144" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="I144" s="25"/>
-      <c r="J144" s="25"/>
+      <c r="I144" s="27"/>
+      <c r="J144" s="27"/>
       <c r="K144" s="26"/>
-      <c r="L144" s="23"/>
+      <c r="L144" s="46"/>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A145" s="26"/>
-      <c r="B145" s="24"/>
+      <c r="B145" s="28"/>
       <c r="C145" s="26"/>
       <c r="D145" s="26"/>
-      <c r="E145" s="24"/>
-      <c r="F145" s="25"/>
-      <c r="G145" s="25"/>
+      <c r="E145" s="28"/>
+      <c r="F145" s="27"/>
+      <c r="G145" s="27"/>
       <c r="H145" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="I145" s="25"/>
-      <c r="J145" s="25"/>
+      <c r="I145" s="27"/>
+      <c r="J145" s="27"/>
       <c r="K145" s="26"/>
-      <c r="L145" s="23"/>
+      <c r="L145" s="46"/>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A146" s="26"/>
-      <c r="B146" s="24"/>
+      <c r="B146" s="28"/>
       <c r="C146" s="26"/>
       <c r="D146" s="26"/>
-      <c r="E146" s="24"/>
-      <c r="F146" s="25"/>
-      <c r="G146" s="25"/>
+      <c r="E146" s="28"/>
+      <c r="F146" s="27"/>
+      <c r="G146" s="27"/>
       <c r="H146" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="I146" s="25"/>
-      <c r="J146" s="25"/>
+      <c r="I146" s="27"/>
+      <c r="J146" s="27"/>
       <c r="K146" s="26"/>
-      <c r="L146" s="23"/>
+      <c r="L146" s="46"/>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A147" s="26"/>
-      <c r="B147" s="24"/>
+      <c r="B147" s="28"/>
       <c r="C147" s="26"/>
       <c r="D147" s="26"/>
-      <c r="E147" s="24"/>
-      <c r="F147" s="25"/>
-      <c r="G147" s="25"/>
+      <c r="E147" s="28"/>
+      <c r="F147" s="27"/>
+      <c r="G147" s="27"/>
       <c r="H147" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="I147" s="25"/>
-      <c r="J147" s="25"/>
+      <c r="I147" s="27"/>
+      <c r="J147" s="27"/>
       <c r="K147" s="26"/>
-      <c r="L147" s="23"/>
+      <c r="L147" s="46"/>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A148" s="26"/>
-      <c r="B148" s="24"/>
+      <c r="B148" s="28"/>
       <c r="C148" s="26"/>
       <c r="D148" s="26"/>
-      <c r="E148" s="24"/>
-      <c r="F148" s="25"/>
-      <c r="G148" s="25"/>
+      <c r="E148" s="28"/>
+      <c r="F148" s="27"/>
+      <c r="G148" s="27"/>
       <c r="H148" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="I148" s="25"/>
-      <c r="J148" s="25"/>
+      <c r="I148" s="27"/>
+      <c r="J148" s="27"/>
       <c r="K148" s="26"/>
-      <c r="L148" s="23"/>
+      <c r="L148" s="46"/>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A149" s="26" t="s">
         <v>272</v>
       </c>
-      <c r="B149" s="24" t="s">
+      <c r="B149" s="28" t="s">
         <v>273</v>
       </c>
       <c r="C149" s="26" t="s">
@@ -4812,198 +4812,223 @@
       <c r="D149" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="E149" s="24" t="s">
+      <c r="E149" s="28" t="s">
         <v>274</v>
       </c>
-      <c r="F149" s="24" t="s">
+      <c r="F149" s="28" t="s">
         <v>275</v>
       </c>
-      <c r="G149" s="24" t="s">
+      <c r="G149" s="28" t="s">
         <v>276</v>
       </c>
       <c r="H149" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="I149" s="24" t="s">
+      <c r="I149" s="28" t="s">
         <v>279</v>
       </c>
-      <c r="J149" s="24" t="s">
+      <c r="J149" s="28" t="s">
         <v>279</v>
       </c>
       <c r="K149" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="L149" s="23"/>
+      <c r="L149" s="46"/>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A150" s="26"/>
-      <c r="B150" s="24"/>
+      <c r="B150" s="28"/>
       <c r="C150" s="26"/>
       <c r="D150" s="26"/>
-      <c r="E150" s="24"/>
-      <c r="F150" s="25"/>
-      <c r="G150" s="25"/>
+      <c r="E150" s="28"/>
+      <c r="F150" s="27"/>
+      <c r="G150" s="27"/>
       <c r="H150" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="I150" s="25"/>
-      <c r="J150" s="25"/>
+      <c r="I150" s="27"/>
+      <c r="J150" s="27"/>
       <c r="K150" s="26"/>
-      <c r="L150" s="23"/>
+      <c r="L150" s="46"/>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A151" s="26"/>
-      <c r="B151" s="24"/>
+      <c r="B151" s="28"/>
       <c r="C151" s="26"/>
       <c r="D151" s="26"/>
-      <c r="E151" s="24"/>
-      <c r="F151" s="25"/>
-      <c r="G151" s="25"/>
+      <c r="E151" s="28"/>
+      <c r="F151" s="27"/>
+      <c r="G151" s="27"/>
       <c r="H151" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="I151" s="25"/>
-      <c r="J151" s="25"/>
+      <c r="I151" s="27"/>
+      <c r="J151" s="27"/>
       <c r="K151" s="26"/>
-      <c r="L151" s="23"/>
+      <c r="L151" s="46"/>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A152" s="26"/>
-      <c r="B152" s="24"/>
+      <c r="B152" s="28"/>
       <c r="C152" s="26"/>
       <c r="D152" s="26"/>
-      <c r="E152" s="24"/>
-      <c r="F152" s="25"/>
-      <c r="G152" s="25"/>
+      <c r="E152" s="28"/>
+      <c r="F152" s="27"/>
+      <c r="G152" s="27"/>
       <c r="H152" s="3"/>
-      <c r="I152" s="25"/>
-      <c r="J152" s="25"/>
+      <c r="I152" s="27"/>
+      <c r="J152" s="27"/>
       <c r="K152" s="26"/>
-      <c r="L152" s="23"/>
+      <c r="L152" s="46"/>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A153" s="26"/>
-      <c r="B153" s="24"/>
+      <c r="B153" s="28"/>
       <c r="C153" s="26"/>
       <c r="D153" s="26"/>
-      <c r="E153" s="24"/>
-      <c r="F153" s="25"/>
-      <c r="G153" s="25"/>
+      <c r="E153" s="28"/>
+      <c r="F153" s="27"/>
+      <c r="G153" s="27"/>
       <c r="H153" s="3"/>
-      <c r="I153" s="25"/>
-      <c r="J153" s="25"/>
+      <c r="I153" s="27"/>
+      <c r="J153" s="27"/>
       <c r="K153" s="26"/>
-      <c r="L153" s="23"/>
+      <c r="L153" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="263">
-    <mergeCell ref="A24:A30"/>
-    <mergeCell ref="B24:B30"/>
-    <mergeCell ref="C24:C30"/>
-    <mergeCell ref="D24:D30"/>
-    <mergeCell ref="E24:E30"/>
-    <mergeCell ref="F24:F30"/>
-    <mergeCell ref="A12:A16"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="C12:C16"/>
-    <mergeCell ref="D12:D16"/>
-    <mergeCell ref="E12:E16"/>
-    <mergeCell ref="F12:F16"/>
-    <mergeCell ref="I12:I16"/>
-    <mergeCell ref="G12:G16"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="C17:C23"/>
-    <mergeCell ref="D17:D23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="I17:I23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="C2:C6"/>
-    <mergeCell ref="D2:D6"/>
-    <mergeCell ref="E2:E6"/>
-    <mergeCell ref="A7:A11"/>
-    <mergeCell ref="B7:B11"/>
-    <mergeCell ref="C7:C11"/>
-    <mergeCell ref="D7:D11"/>
-    <mergeCell ref="E7:E11"/>
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="K17:K23"/>
-    <mergeCell ref="L17:L23"/>
-    <mergeCell ref="J24:J30"/>
-    <mergeCell ref="K24:K30"/>
-    <mergeCell ref="L24:L30"/>
-    <mergeCell ref="F2:F6"/>
-    <mergeCell ref="J12:J16"/>
-    <mergeCell ref="K12:K16"/>
-    <mergeCell ref="L12:L16"/>
-    <mergeCell ref="F7:F11"/>
-    <mergeCell ref="I7:I11"/>
-    <mergeCell ref="G7:G11"/>
-    <mergeCell ref="J7:J11"/>
-    <mergeCell ref="I2:I6"/>
-    <mergeCell ref="G2:G6"/>
-    <mergeCell ref="J2:J6"/>
-    <mergeCell ref="K2:K6"/>
-    <mergeCell ref="L2:L6"/>
-    <mergeCell ref="K7:K11"/>
-    <mergeCell ref="L7:L11"/>
-    <mergeCell ref="I24:I30"/>
-    <mergeCell ref="G24:G30"/>
-    <mergeCell ref="I31:I37"/>
-    <mergeCell ref="J31:J37"/>
-    <mergeCell ref="K31:K37"/>
-    <mergeCell ref="L31:L37"/>
-    <mergeCell ref="B31:B37"/>
-    <mergeCell ref="C31:C37"/>
-    <mergeCell ref="D31:D37"/>
-    <mergeCell ref="E31:E37"/>
-    <mergeCell ref="F31:F37"/>
-    <mergeCell ref="G31:G37"/>
-    <mergeCell ref="A31:A37"/>
-    <mergeCell ref="A42:A50"/>
-    <mergeCell ref="B42:B50"/>
-    <mergeCell ref="C42:C50"/>
-    <mergeCell ref="D42:D50"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="C38:C41"/>
-    <mergeCell ref="D38:D41"/>
-    <mergeCell ref="E51:E60"/>
-    <mergeCell ref="F51:F60"/>
-    <mergeCell ref="G51:G60"/>
-    <mergeCell ref="I51:I60"/>
-    <mergeCell ref="J51:J60"/>
-    <mergeCell ref="K51:K60"/>
-    <mergeCell ref="L51:L60"/>
-    <mergeCell ref="E42:E50"/>
-    <mergeCell ref="F42:F50"/>
-    <mergeCell ref="G42:G50"/>
-    <mergeCell ref="I42:I50"/>
-    <mergeCell ref="J42:J50"/>
-    <mergeCell ref="E79:E85"/>
-    <mergeCell ref="L65:L71"/>
-    <mergeCell ref="A72:A78"/>
-    <mergeCell ref="B72:B78"/>
-    <mergeCell ref="C72:C78"/>
-    <mergeCell ref="D72:D78"/>
-    <mergeCell ref="E72:E78"/>
-    <mergeCell ref="F72:F78"/>
-    <mergeCell ref="I72:I78"/>
-    <mergeCell ref="J72:J78"/>
-    <mergeCell ref="K72:K78"/>
-    <mergeCell ref="L72:L78"/>
-    <mergeCell ref="F65:F71"/>
-    <mergeCell ref="I65:I71"/>
-    <mergeCell ref="J65:J71"/>
-    <mergeCell ref="K65:K71"/>
-    <mergeCell ref="A65:A71"/>
-    <mergeCell ref="B65:B71"/>
-    <mergeCell ref="C65:C71"/>
-    <mergeCell ref="D65:D71"/>
-    <mergeCell ref="E65:E71"/>
+    <mergeCell ref="L149:L153"/>
+    <mergeCell ref="F149:F153"/>
+    <mergeCell ref="G149:G153"/>
+    <mergeCell ref="I149:I153"/>
+    <mergeCell ref="J149:J153"/>
+    <mergeCell ref="K149:K153"/>
+    <mergeCell ref="A149:A153"/>
+    <mergeCell ref="B149:B153"/>
+    <mergeCell ref="C149:C153"/>
+    <mergeCell ref="D149:D153"/>
+    <mergeCell ref="E149:E153"/>
+    <mergeCell ref="L133:L140"/>
+    <mergeCell ref="A141:A148"/>
+    <mergeCell ref="B141:B148"/>
+    <mergeCell ref="C141:C148"/>
+    <mergeCell ref="D141:D148"/>
+    <mergeCell ref="E141:E148"/>
+    <mergeCell ref="F141:F148"/>
+    <mergeCell ref="G141:G148"/>
+    <mergeCell ref="I141:I148"/>
+    <mergeCell ref="J141:J148"/>
+    <mergeCell ref="K141:K148"/>
+    <mergeCell ref="L141:L148"/>
+    <mergeCell ref="F133:F140"/>
+    <mergeCell ref="G133:G140"/>
+    <mergeCell ref="I133:I140"/>
+    <mergeCell ref="J133:J140"/>
+    <mergeCell ref="K133:K140"/>
+    <mergeCell ref="A133:A140"/>
+    <mergeCell ref="B133:B140"/>
+    <mergeCell ref="C133:C140"/>
+    <mergeCell ref="D133:D140"/>
+    <mergeCell ref="E133:E140"/>
+    <mergeCell ref="K38:K41"/>
+    <mergeCell ref="L38:L41"/>
+    <mergeCell ref="A61:A64"/>
+    <mergeCell ref="B61:B64"/>
+    <mergeCell ref="C61:C64"/>
+    <mergeCell ref="D61:D64"/>
+    <mergeCell ref="E61:E64"/>
+    <mergeCell ref="F61:F64"/>
+    <mergeCell ref="G61:G64"/>
+    <mergeCell ref="I61:I64"/>
+    <mergeCell ref="J61:J64"/>
+    <mergeCell ref="K61:K64"/>
+    <mergeCell ref="L61:L64"/>
+    <mergeCell ref="E38:E41"/>
+    <mergeCell ref="F38:F41"/>
+    <mergeCell ref="G38:G41"/>
+    <mergeCell ref="I38:I41"/>
+    <mergeCell ref="J38:J41"/>
+    <mergeCell ref="K42:K50"/>
+    <mergeCell ref="L42:L50"/>
+    <mergeCell ref="A51:A60"/>
+    <mergeCell ref="B51:B60"/>
+    <mergeCell ref="C51:C60"/>
+    <mergeCell ref="D51:D60"/>
+    <mergeCell ref="L127:L132"/>
+    <mergeCell ref="G65:G71"/>
+    <mergeCell ref="G72:G78"/>
+    <mergeCell ref="G93:G98"/>
+    <mergeCell ref="G99:G105"/>
+    <mergeCell ref="G106:G112"/>
+    <mergeCell ref="G86:G92"/>
+    <mergeCell ref="G79:G85"/>
+    <mergeCell ref="F127:F132"/>
+    <mergeCell ref="G127:G132"/>
+    <mergeCell ref="I127:I132"/>
+    <mergeCell ref="J127:J132"/>
+    <mergeCell ref="K127:K132"/>
+    <mergeCell ref="L93:L98"/>
+    <mergeCell ref="L99:L105"/>
+    <mergeCell ref="F93:F98"/>
+    <mergeCell ref="I93:I98"/>
+    <mergeCell ref="J93:J98"/>
+    <mergeCell ref="K93:K98"/>
+    <mergeCell ref="A127:A132"/>
+    <mergeCell ref="B127:B132"/>
+    <mergeCell ref="C127:C132"/>
+    <mergeCell ref="D127:D132"/>
+    <mergeCell ref="E127:E132"/>
+    <mergeCell ref="L120:L122"/>
+    <mergeCell ref="A123:A126"/>
+    <mergeCell ref="B123:B126"/>
+    <mergeCell ref="C123:C126"/>
+    <mergeCell ref="D123:D126"/>
+    <mergeCell ref="E123:E126"/>
+    <mergeCell ref="F123:F126"/>
+    <mergeCell ref="G123:G126"/>
+    <mergeCell ref="I123:I126"/>
+    <mergeCell ref="J123:J126"/>
+    <mergeCell ref="K123:K126"/>
+    <mergeCell ref="L123:L126"/>
+    <mergeCell ref="F120:F122"/>
+    <mergeCell ref="G120:G122"/>
+    <mergeCell ref="I120:I122"/>
+    <mergeCell ref="J120:J122"/>
+    <mergeCell ref="K120:K122"/>
+    <mergeCell ref="A120:A122"/>
+    <mergeCell ref="B120:B122"/>
+    <mergeCell ref="F106:F112"/>
+    <mergeCell ref="I106:I112"/>
+    <mergeCell ref="J106:J112"/>
+    <mergeCell ref="K106:K112"/>
+    <mergeCell ref="A106:A112"/>
+    <mergeCell ref="B106:B112"/>
+    <mergeCell ref="C106:C112"/>
+    <mergeCell ref="D106:D112"/>
+    <mergeCell ref="E106:E112"/>
+    <mergeCell ref="C120:C122"/>
+    <mergeCell ref="D120:D122"/>
+    <mergeCell ref="E120:E122"/>
+    <mergeCell ref="L113:L119"/>
+    <mergeCell ref="A113:A119"/>
+    <mergeCell ref="B113:B119"/>
+    <mergeCell ref="C113:C119"/>
+    <mergeCell ref="D113:D119"/>
+    <mergeCell ref="E113:E119"/>
+    <mergeCell ref="F113:F119"/>
+    <mergeCell ref="G113:G119"/>
+    <mergeCell ref="I113:I119"/>
+    <mergeCell ref="J113:J119"/>
+    <mergeCell ref="K113:K119"/>
+    <mergeCell ref="A99:A105"/>
+    <mergeCell ref="B99:B105"/>
+    <mergeCell ref="C99:C105"/>
+    <mergeCell ref="D99:D105"/>
+    <mergeCell ref="E99:E105"/>
+    <mergeCell ref="F99:F105"/>
+    <mergeCell ref="I99:I105"/>
+    <mergeCell ref="J99:J105"/>
+    <mergeCell ref="K99:K105"/>
     <mergeCell ref="A93:A98"/>
     <mergeCell ref="B93:B98"/>
     <mergeCell ref="C93:C98"/>
@@ -5028,138 +5053,113 @@
     <mergeCell ref="B79:B85"/>
     <mergeCell ref="C79:C85"/>
     <mergeCell ref="D79:D85"/>
-    <mergeCell ref="A99:A105"/>
-    <mergeCell ref="B99:B105"/>
-    <mergeCell ref="C99:C105"/>
-    <mergeCell ref="D99:D105"/>
-    <mergeCell ref="E99:E105"/>
-    <mergeCell ref="F99:F105"/>
-    <mergeCell ref="I99:I105"/>
-    <mergeCell ref="J99:J105"/>
-    <mergeCell ref="K99:K105"/>
-    <mergeCell ref="C120:C122"/>
-    <mergeCell ref="D120:D122"/>
-    <mergeCell ref="E120:E122"/>
-    <mergeCell ref="L113:L119"/>
-    <mergeCell ref="A113:A119"/>
-    <mergeCell ref="B113:B119"/>
-    <mergeCell ref="C113:C119"/>
-    <mergeCell ref="D113:D119"/>
-    <mergeCell ref="E113:E119"/>
-    <mergeCell ref="F113:F119"/>
-    <mergeCell ref="G113:G119"/>
-    <mergeCell ref="I113:I119"/>
-    <mergeCell ref="J113:J119"/>
-    <mergeCell ref="K113:K119"/>
-    <mergeCell ref="F106:F112"/>
-    <mergeCell ref="I106:I112"/>
-    <mergeCell ref="J106:J112"/>
-    <mergeCell ref="K106:K112"/>
-    <mergeCell ref="A106:A112"/>
-    <mergeCell ref="B106:B112"/>
-    <mergeCell ref="C106:C112"/>
-    <mergeCell ref="D106:D112"/>
-    <mergeCell ref="E106:E112"/>
-    <mergeCell ref="A127:A132"/>
-    <mergeCell ref="B127:B132"/>
-    <mergeCell ref="C127:C132"/>
-    <mergeCell ref="D127:D132"/>
-    <mergeCell ref="E127:E132"/>
-    <mergeCell ref="L120:L122"/>
-    <mergeCell ref="A123:A126"/>
-    <mergeCell ref="B123:B126"/>
-    <mergeCell ref="C123:C126"/>
-    <mergeCell ref="D123:D126"/>
-    <mergeCell ref="E123:E126"/>
-    <mergeCell ref="F123:F126"/>
-    <mergeCell ref="G123:G126"/>
-    <mergeCell ref="I123:I126"/>
-    <mergeCell ref="J123:J126"/>
-    <mergeCell ref="K123:K126"/>
-    <mergeCell ref="L123:L126"/>
-    <mergeCell ref="F120:F122"/>
-    <mergeCell ref="G120:G122"/>
-    <mergeCell ref="I120:I122"/>
-    <mergeCell ref="J120:J122"/>
-    <mergeCell ref="K120:K122"/>
-    <mergeCell ref="A120:A122"/>
-    <mergeCell ref="B120:B122"/>
-    <mergeCell ref="L127:L132"/>
-    <mergeCell ref="G65:G71"/>
-    <mergeCell ref="G72:G78"/>
-    <mergeCell ref="G93:G98"/>
-    <mergeCell ref="G99:G105"/>
-    <mergeCell ref="G106:G112"/>
-    <mergeCell ref="G86:G92"/>
-    <mergeCell ref="G79:G85"/>
-    <mergeCell ref="F127:F132"/>
-    <mergeCell ref="G127:G132"/>
-    <mergeCell ref="I127:I132"/>
-    <mergeCell ref="J127:J132"/>
-    <mergeCell ref="K127:K132"/>
-    <mergeCell ref="L93:L98"/>
-    <mergeCell ref="L99:L105"/>
-    <mergeCell ref="F93:F98"/>
-    <mergeCell ref="I93:I98"/>
-    <mergeCell ref="J93:J98"/>
-    <mergeCell ref="K93:K98"/>
-    <mergeCell ref="K38:K41"/>
-    <mergeCell ref="L38:L41"/>
-    <mergeCell ref="A61:A64"/>
-    <mergeCell ref="B61:B64"/>
-    <mergeCell ref="C61:C64"/>
-    <mergeCell ref="D61:D64"/>
-    <mergeCell ref="E61:E64"/>
-    <mergeCell ref="F61:F64"/>
-    <mergeCell ref="G61:G64"/>
-    <mergeCell ref="I61:I64"/>
-    <mergeCell ref="J61:J64"/>
-    <mergeCell ref="K61:K64"/>
-    <mergeCell ref="L61:L64"/>
-    <mergeCell ref="E38:E41"/>
-    <mergeCell ref="F38:F41"/>
-    <mergeCell ref="G38:G41"/>
-    <mergeCell ref="I38:I41"/>
-    <mergeCell ref="J38:J41"/>
-    <mergeCell ref="K42:K50"/>
-    <mergeCell ref="L42:L50"/>
-    <mergeCell ref="A51:A60"/>
-    <mergeCell ref="B51:B60"/>
-    <mergeCell ref="C51:C60"/>
-    <mergeCell ref="D51:D60"/>
-    <mergeCell ref="L133:L140"/>
-    <mergeCell ref="A141:A148"/>
-    <mergeCell ref="B141:B148"/>
-    <mergeCell ref="C141:C148"/>
-    <mergeCell ref="D141:D148"/>
-    <mergeCell ref="E141:E148"/>
-    <mergeCell ref="F141:F148"/>
-    <mergeCell ref="G141:G148"/>
-    <mergeCell ref="I141:I148"/>
-    <mergeCell ref="J141:J148"/>
-    <mergeCell ref="K141:K148"/>
-    <mergeCell ref="L141:L148"/>
-    <mergeCell ref="F133:F140"/>
-    <mergeCell ref="G133:G140"/>
-    <mergeCell ref="I133:I140"/>
-    <mergeCell ref="J133:J140"/>
-    <mergeCell ref="K133:K140"/>
-    <mergeCell ref="A133:A140"/>
-    <mergeCell ref="B133:B140"/>
-    <mergeCell ref="C133:C140"/>
-    <mergeCell ref="D133:D140"/>
-    <mergeCell ref="E133:E140"/>
-    <mergeCell ref="L149:L153"/>
-    <mergeCell ref="F149:F153"/>
-    <mergeCell ref="G149:G153"/>
-    <mergeCell ref="I149:I153"/>
-    <mergeCell ref="J149:J153"/>
-    <mergeCell ref="K149:K153"/>
-    <mergeCell ref="A149:A153"/>
-    <mergeCell ref="B149:B153"/>
-    <mergeCell ref="C149:C153"/>
-    <mergeCell ref="D149:D153"/>
-    <mergeCell ref="E149:E153"/>
+    <mergeCell ref="E79:E85"/>
+    <mergeCell ref="L65:L71"/>
+    <mergeCell ref="A72:A78"/>
+    <mergeCell ref="B72:B78"/>
+    <mergeCell ref="C72:C78"/>
+    <mergeCell ref="D72:D78"/>
+    <mergeCell ref="E72:E78"/>
+    <mergeCell ref="F72:F78"/>
+    <mergeCell ref="I72:I78"/>
+    <mergeCell ref="J72:J78"/>
+    <mergeCell ref="K72:K78"/>
+    <mergeCell ref="L72:L78"/>
+    <mergeCell ref="F65:F71"/>
+    <mergeCell ref="I65:I71"/>
+    <mergeCell ref="J65:J71"/>
+    <mergeCell ref="K65:K71"/>
+    <mergeCell ref="A65:A71"/>
+    <mergeCell ref="B65:B71"/>
+    <mergeCell ref="C65:C71"/>
+    <mergeCell ref="D65:D71"/>
+    <mergeCell ref="E65:E71"/>
+    <mergeCell ref="E51:E60"/>
+    <mergeCell ref="F51:F60"/>
+    <mergeCell ref="G51:G60"/>
+    <mergeCell ref="I51:I60"/>
+    <mergeCell ref="J51:J60"/>
+    <mergeCell ref="K51:K60"/>
+    <mergeCell ref="L51:L60"/>
+    <mergeCell ref="E42:E50"/>
+    <mergeCell ref="F42:F50"/>
+    <mergeCell ref="G42:G50"/>
+    <mergeCell ref="I42:I50"/>
+    <mergeCell ref="J42:J50"/>
+    <mergeCell ref="A31:A37"/>
+    <mergeCell ref="A42:A50"/>
+    <mergeCell ref="B42:B50"/>
+    <mergeCell ref="C42:C50"/>
+    <mergeCell ref="D42:D50"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="C38:C41"/>
+    <mergeCell ref="D38:D41"/>
+    <mergeCell ref="I31:I37"/>
+    <mergeCell ref="J31:J37"/>
+    <mergeCell ref="K31:K37"/>
+    <mergeCell ref="L31:L37"/>
+    <mergeCell ref="B31:B37"/>
+    <mergeCell ref="C31:C37"/>
+    <mergeCell ref="D31:D37"/>
+    <mergeCell ref="E31:E37"/>
+    <mergeCell ref="F31:F37"/>
+    <mergeCell ref="G31:G37"/>
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="K17:K23"/>
+    <mergeCell ref="L17:L23"/>
+    <mergeCell ref="J24:J30"/>
+    <mergeCell ref="K24:K30"/>
+    <mergeCell ref="L24:L30"/>
+    <mergeCell ref="F2:F6"/>
+    <mergeCell ref="J12:J16"/>
+    <mergeCell ref="K12:K16"/>
+    <mergeCell ref="L12:L16"/>
+    <mergeCell ref="F7:F11"/>
+    <mergeCell ref="I7:I11"/>
+    <mergeCell ref="G7:G11"/>
+    <mergeCell ref="J7:J11"/>
+    <mergeCell ref="I2:I6"/>
+    <mergeCell ref="G2:G6"/>
+    <mergeCell ref="J2:J6"/>
+    <mergeCell ref="K2:K6"/>
+    <mergeCell ref="L2:L6"/>
+    <mergeCell ref="K7:K11"/>
+    <mergeCell ref="L7:L11"/>
+    <mergeCell ref="I24:I30"/>
+    <mergeCell ref="G24:G30"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="D2:D6"/>
+    <mergeCell ref="E2:E6"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="C7:C11"/>
+    <mergeCell ref="D7:D11"/>
+    <mergeCell ref="E7:E11"/>
+    <mergeCell ref="I12:I16"/>
+    <mergeCell ref="G12:G16"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="C17:C23"/>
+    <mergeCell ref="D17:D23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="I17:I23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="A24:A30"/>
+    <mergeCell ref="B24:B30"/>
+    <mergeCell ref="C24:C30"/>
+    <mergeCell ref="D24:D30"/>
+    <mergeCell ref="E24:E30"/>
+    <mergeCell ref="F24:F30"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="C12:C16"/>
+    <mergeCell ref="D12:D16"/>
+    <mergeCell ref="E12:E16"/>
+    <mergeCell ref="F12:F16"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2 K7 K12 K17 K24 K31 K42 K51 K65 K72 K79 K86 K93 K99 K127 K106 K113 K123 K120 K38 K61 K133 K141 K149" xr:uid="{74B702DF-E2A1-434C-BE99-FD058BB443D1}">
